--- a/docs/menuItems.xlsx
+++ b/docs/menuItems.xlsx
@@ -24,7 +24,7 @@
     <author>Carsten</author>
   </authors>
   <commentList>
-    <comment ref="C13" authorId="0" shapeId="0">
+    <comment ref="C12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="200">
   <si>
     <t>Index #</t>
   </si>
@@ -145,15 +145,9 @@
     <t>savePreset</t>
   </si>
   <si>
-    <t xml:space="preserve">LED Dimmer   </t>
-  </si>
-  <si>
     <t>Bootld Update</t>
   </si>
   <si>
-    <t xml:space="preserve">Preset Init  </t>
-  </si>
-  <si>
     <t xml:space="preserve">MIDI CC Set  </t>
   </si>
   <si>
@@ -307,15 +301,6 @@
     <t>GM Harm1</t>
   </si>
   <si>
-    <t>Upper GM Synth</t>
-  </si>
-  <si>
-    <t>Lower GM Synth</t>
-  </si>
-  <si>
-    <t>Pedal GM Synth</t>
-  </si>
-  <si>
     <t>Upper ADSR</t>
   </si>
   <si>
@@ -592,9 +577,6 @@
     <t>enterBootloader</t>
   </si>
   <si>
-    <t xml:space="preserve">Preset Name  </t>
-  </si>
-  <si>
     <t>enterPresetName</t>
   </si>
   <si>
@@ -643,7 +625,34 @@
     <t>Perc Level</t>
   </si>
   <si>
-    <t>Main</t>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>Preset Init</t>
+  </si>
+  <si>
+    <t>Preset Name</t>
+  </si>
+  <si>
+    <t>Lower GM</t>
+  </si>
+  <si>
+    <t>Pedal GM</t>
+  </si>
+  <si>
+    <t>Upper GM</t>
+  </si>
+  <si>
+    <t>midich</t>
+  </si>
+  <si>
+    <t>enterScreenSaver</t>
+  </si>
+  <si>
+    <t>LED Dimmer</t>
+  </si>
+  <si>
+    <t>Screen Saver</t>
   </si>
 </sst>
 </file>
@@ -814,19 +823,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F8E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF66FF66"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -863,6 +860,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF66FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -956,9 +965,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -971,22 +977,19 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1013,6 +1016,12 @@
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1024,8 +1033,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCFF66"/>
+      <color rgb="FFCCFF99"/>
+      <color rgb="FF66FFFF"/>
       <color rgb="FFFF99FF"/>
-      <color rgb="FF66FFFF"/>
       <color rgb="FFFFFFCC"/>
     </mruColors>
   </colors>
@@ -1327,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P207"/>
+  <dimension ref="A1:P208"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="20" customWidth="1"/>
@@ -1353,13 +1364,13 @@
         <v>5</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E1" s="44" t="s">
-        <v>157</v>
+        <v>49</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>152</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>3</v>
@@ -1368,16 +1379,16 @@
         <v>4</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J1" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="21" t="s">
         <v>47</v>
-      </c>
-      <c r="K1" s="21" t="s">
-        <v>49</v>
       </c>
       <c r="L1" s="22" t="s">
         <v>10</v>
@@ -1397,18 +1408,20 @@
       <c r="A2" s="16">
         <v>0</v>
       </c>
-      <c r="B2" s="27" t="s">
-        <v>196</v>
+      <c r="B2" s="44" t="s">
+        <v>22</v>
       </c>
       <c r="C2" s="17">
-        <v>-1</v>
+        <f>A202</f>
+        <v>200</v>
       </c>
       <c r="D2" s="17">
-        <v>-1</v>
-      </c>
-      <c r="E2" s="43">
+        <f>A203</f>
+        <v>201</v>
+      </c>
+      <c r="E2" s="41">
         <f>D2-C2+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="7">
         <v>0</v>
@@ -1423,14 +1436,14 @@
         <v>268</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>29</v>
       </c>
       <c r="L2" s="11" t="str">
         <f>CONCATENATE("""",B2,""", ")</f>
-        <v xml:space="preserve">"Main", </v>
+        <v xml:space="preserve">"Preset", </v>
       </c>
       <c r="M2" s="11" t="str">
         <f>IF(K2="NULL",CONCATENATE(K2,", "),CONCATENATE("&amp;",K2,", "))</f>
@@ -1438,11 +1451,11 @@
       </c>
       <c r="N2" s="11" t="str">
         <f>IF(J2="NULL",CONCATENATE(J2,", "),CONCATENATE("tm_",J2,", "))</f>
-        <v xml:space="preserve">tm_organ, </v>
+        <v xml:space="preserve">tm_preset, </v>
       </c>
       <c r="O2" s="10" t="str">
         <f>CONCATENATE("  {",L2,C2,", ",D2,", ",I2,", ",M2,N2,F2,", ",G2,", ",H2,"},  // Idx ", A2)</f>
-        <v xml:space="preserve">  {"Main", -1, -1, 268, &amp;savePreset, tm_organ, 0, 99, 0},  // Idx 0</v>
+        <v xml:space="preserve">  {"Preset", 200, 201, 268, &amp;savePreset, tm_preset, 0, 99, 0},  // Idx 0</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1451,75 +1464,75 @@
         <f>A2+1</f>
         <v>1</v>
       </c>
-      <c r="B3" s="27" t="s">
-        <v>22</v>
+      <c r="B3" s="29" t="s">
+        <v>12</v>
       </c>
       <c r="C3" s="17">
-        <f>A202</f>
-        <v>200</v>
+        <f>A28</f>
+        <v>26</v>
       </c>
       <c r="D3" s="17">
-        <f>A206</f>
-        <v>204</v>
-      </c>
-      <c r="E3" s="43">
-        <f>D3-C3+1</f>
-        <v>5</v>
-      </c>
-      <c r="F3" s="7">
+        <f>A39</f>
+        <v>37</v>
+      </c>
+      <c r="E3" s="41">
+        <f t="shared" ref="E3:E20" si="0">D3-C3+1</f>
+        <v>12</v>
+      </c>
+      <c r="F3" s="3">
         <v>0</v>
       </c>
       <c r="G3" s="7">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="H3" s="7">
         <v>0</v>
       </c>
       <c r="I3" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="L3" s="11" t="str">
-        <f>CONCATENATE("""",B3,""", ")</f>
-        <v xml:space="preserve">"Preset", </v>
+        <f t="shared" ref="L3:L11" si="1">CONCATENATE("""",B3,""", ")</f>
+        <v xml:space="preserve">"Upper Voice", </v>
       </c>
       <c r="M3" s="11" t="str">
-        <f>IF(K3="NULL",CONCATENATE(K3,", "),CONCATENATE("&amp;",K3,", "))</f>
-        <v xml:space="preserve">&amp;savePreset, </v>
+        <f t="shared" ref="M3:M11" si="2">IF(K3="NULL",CONCATENATE(K3,", "),CONCATENATE("&amp;",K3,", "))</f>
+        <v xml:space="preserve">&amp;saveUpper, </v>
       </c>
       <c r="N3" s="11" t="str">
-        <f>IF(J3="NULL",CONCATENATE(J3,", "),CONCATENATE("tm_",J3,", "))</f>
-        <v xml:space="preserve">tm_preset, </v>
+        <f t="shared" ref="N3:N34" si="3">IF(J3="NULL",CONCATENATE(J3,", "),CONCATENATE("tm_",J3,", "))</f>
+        <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O3" s="10" t="str">
-        <f>CONCATENATE("  {",L3,C3,", ",D3,", ",I3,", ",M3,N3,F3,", ",G3,", ",H3,"},  // Idx ", A3)</f>
-        <v xml:space="preserve">  {"Preset", 200, 204, 268, &amp;savePreset, tm_preset, 0, 99, 0},  // Idx 1</v>
+        <f t="shared" ref="O3:O34" si="4">CONCATENATE("  {",L3,C3,", ",D3,", ",I3,", ",M3,N3,F3,", ",G3,", ",H3,"},  // Idx ", A3)</f>
+        <v xml:space="preserve">  {"Upper Voice", 26, 37, 269, &amp;saveUpper, tm_numeric, 0, 15, 0},  // Idx 1</v>
       </c>
       <c r="P3" s="6"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
-        <f>A3+1</f>
+        <f t="shared" ref="A4:A21" si="5">A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="30" t="s">
-        <v>12</v>
+      <c r="B4" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="C4" s="17">
-        <f>A28</f>
-        <v>26</v>
+        <f>A76</f>
+        <v>74</v>
       </c>
       <c r="D4" s="17">
-        <f>A39</f>
-        <v>37</v>
-      </c>
-      <c r="E4" s="43">
-        <f t="shared" ref="E4:E21" si="0">D4-C4+1</f>
+        <f>A87</f>
+        <v>85</v>
+      </c>
+      <c r="E4" s="41">
+        <f>D4-C4+1</f>
         <v>12</v>
       </c>
       <c r="F4" s="3">
@@ -1532,51 +1545,51 @@
         <v>0</v>
       </c>
       <c r="I4" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>26</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="L4" s="11" t="str">
-        <f t="shared" ref="L4:L12" si="1">CONCATENATE("""",B4,""", ")</f>
-        <v xml:space="preserve">"Upper Voice", </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"Lower Voice", </v>
       </c>
       <c r="M4" s="11" t="str">
-        <f t="shared" ref="M4:M12" si="2">IF(K4="NULL",CONCATENATE(K4,", "),CONCATENATE("&amp;",K4,", "))</f>
-        <v xml:space="preserve">&amp;saveUpper, </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">&amp;saveLower, </v>
       </c>
       <c r="N4" s="11" t="str">
-        <f t="shared" ref="N4:N34" si="3">IF(J4="NULL",CONCATENATE(J4,", "),CONCATENATE("tm_",J4,", "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O4" s="10" t="str">
-        <f t="shared" ref="O4:O34" si="4">CONCATENATE("  {",L4,C4,", ",D4,", ",I4,", ",M4,N4,F4,", ",G4,", ",H4,"},  // Idx ", A4)</f>
-        <v xml:space="preserve">  {"Upper Voice", 26, 37, 269, &amp;saveUpper, tm_numeric, 0, 15, 0},  // Idx 2</v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">  {"Lower Voice", 74, 85, 270, &amp;saveLower, tm_numeric, 0, 15, 0},  // Idx 2</v>
       </c>
       <c r="P4" s="6"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
-        <f t="shared" ref="A5:A23" si="5">A4+1</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>13</v>
+      <c r="B5" s="27" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="17">
-        <f>A76</f>
-        <v>74</v>
+        <f>A112</f>
+        <v>110</v>
       </c>
       <c r="D5" s="17">
-        <f>A87</f>
-        <v>85</v>
-      </c>
-      <c r="E5" s="43">
+        <f>A116</f>
+        <v>114</v>
+      </c>
+      <c r="E5" s="41">
         <f>D5-C5+1</f>
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F5" s="3">
         <v>0</v>
@@ -1588,21 +1601,21 @@
         <v>0</v>
       </c>
       <c r="I5" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>26</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L5" s="11" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">"Lower Voice", </v>
+        <v xml:space="preserve">"Pedal Voice", </v>
       </c>
       <c r="M5" s="11" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">&amp;saveLower, </v>
+        <v xml:space="preserve">&amp;savePedal, </v>
       </c>
       <c r="N5" s="11" t="str">
         <f t="shared" si="3"/>
@@ -1610,7 +1623,7 @@
       </c>
       <c r="O5" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Lower Voice", 74, 85, 270, &amp;saveLower, tm_numeric, 0, 15, 0},  // Idx 3</v>
+        <v xml:space="preserve">  {"Pedal Voice", 110, 114, 271, &amp;savePedal, tm_numeric, 0, 15, 0},  // Idx 3</v>
       </c>
       <c r="P5" s="6"/>
     </row>
@@ -1620,53 +1633,53 @@
         <v>4</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C6" s="17">
-        <f>A112</f>
-        <v>110</v>
+        <f>A129</f>
+        <v>127</v>
       </c>
       <c r="D6" s="17">
-        <f>A116</f>
-        <v>114</v>
-      </c>
-      <c r="E6" s="43">
+        <f>A140</f>
+        <v>138</v>
+      </c>
+      <c r="E6" s="41">
         <f>D6-C6+1</f>
-        <v>5</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="7">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="F6" s="7">
+        <v>-1</v>
+      </c>
+      <c r="G6" s="18">
+        <v>-1</v>
       </c>
       <c r="H6" s="7">
         <v>0</v>
       </c>
-      <c r="I6" s="7">
-        <v>271</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>26</v>
+      <c r="I6" s="18">
+        <v>-1</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>174</v>
+        <v>8</v>
       </c>
       <c r="L6" s="11" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">"Pedal Voice", </v>
+        <v xml:space="preserve">"Tabs", </v>
       </c>
       <c r="M6" s="11" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">&amp;savePedal, </v>
+        <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N6" s="11" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">tm_numeric, </v>
+        <v xml:space="preserve">tm_none, </v>
       </c>
       <c r="O6" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Pedal Voice", 110, 114, 271, &amp;savePedal, tm_numeric, 0, 15, 0},  // Idx 4</v>
+        <v xml:space="preserve">  {"Tabs", 127, 138, -1, NULL, tm_none, -1, -1, 0},  // Idx 4</v>
       </c>
       <c r="P6" s="6"/>
     </row>
@@ -1675,42 +1688,42 @@
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="17">
-        <f>A129</f>
-        <v>127</v>
-      </c>
-      <c r="D7" s="17">
-        <f>A140</f>
-        <v>138</v>
-      </c>
-      <c r="E7" s="43">
-        <f>D7-C7+1</f>
-        <v>12</v>
-      </c>
-      <c r="F7" s="7">
-        <v>-1</v>
-      </c>
-      <c r="G7" s="18">
-        <v>-1</v>
+      <c r="B7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="13">
+        <f>A24</f>
+        <v>22</v>
+      </c>
+      <c r="D7" s="13">
+        <f>A26</f>
+        <v>24</v>
+      </c>
+      <c r="E7" s="41">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2</v>
       </c>
       <c r="H7" s="7">
         <v>0</v>
       </c>
-      <c r="I7" s="18">
-        <v>-1</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>24</v>
+      <c r="I7" s="7">
+        <v>256</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L7" s="11" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">"Tabs", </v>
+        <v xml:space="preserve">"Rotary Speed", </v>
       </c>
       <c r="M7" s="11" t="str">
         <f t="shared" si="2"/>
@@ -1718,11 +1731,11 @@
       </c>
       <c r="N7" s="11" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">tm_none, </v>
+        <v xml:space="preserve">tm_halfmoon, </v>
       </c>
       <c r="O7" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Tabs", 127, 138, -1, NULL, tm_none, -1, -1, 0},  // Idx 5</v>
+        <v xml:space="preserve">  {"Rotary Speed", 22, 24, 256, NULL, tm_halfmoon, 0, 2, 0},  // Idx 5</v>
       </c>
       <c r="P7" s="6"/>
     </row>
@@ -1731,42 +1744,42 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>42</v>
+      <c r="B8" s="26" t="s">
+        <v>6</v>
       </c>
       <c r="C8" s="13">
-        <f>A24</f>
-        <v>22</v>
+        <f>A22</f>
+        <v>20</v>
       </c>
       <c r="D8" s="13">
-        <f>A26</f>
-        <v>24</v>
-      </c>
-      <c r="E8" s="43">
+        <f>A23</f>
+        <v>21</v>
+      </c>
+      <c r="E8" s="41">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
       </c>
       <c r="G8" s="3">
-        <v>2</v>
+        <v>127</v>
       </c>
       <c r="H8" s="7">
         <v>0</v>
       </c>
-      <c r="I8" s="7">
-        <v>256</v>
+      <c r="I8" s="5">
+        <v>80</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L8" s="11" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">"Rotary Speed", </v>
+        <v xml:space="preserve">"Master Volume", </v>
       </c>
       <c r="M8" s="11" t="str">
         <f t="shared" si="2"/>
@@ -1774,11 +1787,11 @@
       </c>
       <c r="N8" s="11" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">tm_halfmoon, </v>
+        <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O8" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Rotary Speed", 22, 24, 256, NULL, tm_halfmoon, 0, 2, 0},  // Idx 6</v>
+        <v xml:space="preserve">  {"Master Volume", 20, 21, 80, NULL, tm_pot, 0, 127, 0},  // Idx 6</v>
       </c>
       <c r="P8" s="6"/>
     </row>
@@ -1787,20 +1800,20 @@
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>6</v>
+      <c r="B9" s="43" t="s">
+        <v>7</v>
       </c>
       <c r="C9" s="13">
-        <f>A22</f>
-        <v>20</v>
+        <f>A27</f>
+        <v>25</v>
       </c>
       <c r="D9" s="13">
-        <f>A23</f>
-        <v>21</v>
-      </c>
-      <c r="E9" s="43">
+        <f>A27</f>
+        <v>25</v>
+      </c>
+      <c r="E9" s="41">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -1812,17 +1825,17 @@
         <v>0</v>
       </c>
       <c r="I9" s="5">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L9" s="11" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">"Master Volume", </v>
+        <v xml:space="preserve">"Amp Gain", </v>
       </c>
       <c r="M9" s="11" t="str">
         <f t="shared" si="2"/>
@@ -1834,7 +1847,7 @@
       </c>
       <c r="O9" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Master Volume", 20, 21, 80, NULL, tm_pot, 0, 127, 0},  // Idx 7</v>
+        <v xml:space="preserve">  {"Amp Gain", 25, 25, 81, NULL, tm_pot, 0, 127, 0},  // Idx 7</v>
       </c>
       <c r="P9" s="6"/>
     </row>
@@ -1843,42 +1856,42 @@
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="B10" s="45" t="s">
-        <v>7</v>
+      <c r="B10" s="34" t="s">
+        <v>42</v>
       </c>
       <c r="C10" s="13">
-        <f>A27</f>
-        <v>25</v>
+        <f>A163</f>
+        <v>161</v>
       </c>
       <c r="D10" s="13">
-        <f>A27</f>
-        <v>25</v>
-      </c>
-      <c r="E10" s="43">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>A165</f>
+        <v>163</v>
+      </c>
+      <c r="E10" s="41">
+        <f t="shared" ref="E10:E17" si="6">D10-C10+1</f>
+        <v>3</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
       </c>
       <c r="G10" s="3">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="H10" s="7">
         <v>0</v>
       </c>
       <c r="I10" s="5">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>146</v>
+        <v>26</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L10" s="11" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">"Amp Gain", </v>
+        <v xml:space="preserve">"Reverb Prgm", </v>
       </c>
       <c r="M10" s="11" t="str">
         <f t="shared" si="2"/>
@@ -1886,11 +1899,11 @@
       </c>
       <c r="N10" s="11" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">tm_pot, </v>
+        <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O10" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Amp Gain", 25, 25, 81, NULL, tm_pot, 0, 127, 0},  // Idx 8</v>
+        <v xml:space="preserve">  {"Reverb Prgm", 161, 163, 263, NULL, tm_numeric, 0, 3, 0},  // Idx 8</v>
       </c>
       <c r="P10" s="6"/>
     </row>
@@ -1899,42 +1912,42 @@
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="B11" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="13">
-        <f>A163</f>
-        <v>161</v>
-      </c>
-      <c r="D11" s="13">
-        <f>A165</f>
-        <v>163</v>
-      </c>
-      <c r="E11" s="43">
-        <f t="shared" ref="E11:E18" si="6">D11-C11+1</f>
-        <v>3</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3">
-        <v>3</v>
+      <c r="B11" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="17">
+        <f>A166</f>
+        <v>164</v>
+      </c>
+      <c r="D11" s="17">
+        <f>A176</f>
+        <v>174</v>
+      </c>
+      <c r="E11" s="41">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="F11" s="7">
+        <v>-1</v>
+      </c>
+      <c r="G11" s="18">
+        <v>-1</v>
       </c>
       <c r="H11" s="7">
         <v>0</v>
       </c>
-      <c r="I11" s="5">
-        <v>263</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" s="7" t="s">
+      <c r="I11" s="18">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="18" t="s">
         <v>8</v>
       </c>
       <c r="L11" s="11" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">"Reverb Prgm", </v>
+        <v xml:space="preserve">"Equalizer", </v>
       </c>
       <c r="M11" s="11" t="str">
         <f t="shared" si="2"/>
@@ -1942,11 +1955,11 @@
       </c>
       <c r="N11" s="11" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">tm_numeric, </v>
+        <v xml:space="preserve">tm_none, </v>
       </c>
       <c r="O11" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Reverb Prgm", 161, 163, 263, NULL, tm_numeric, 0, 3, 0},  // Idx 9</v>
+        <v xml:space="preserve">  {"Equalizer", 164, 174, -1, NULL, tm_none, -1, -1, 0},  // Idx 9</v>
       </c>
       <c r="P11" s="6"/>
     </row>
@@ -1955,20 +1968,20 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="B12" s="33" t="s">
-        <v>53</v>
+      <c r="B12" s="29" t="s">
+        <v>82</v>
       </c>
       <c r="C12" s="17">
-        <f>A166</f>
-        <v>164</v>
+        <f>A47</f>
+        <v>45</v>
       </c>
       <c r="D12" s="17">
-        <f>A176</f>
-        <v>174</v>
-      </c>
-      <c r="E12" s="43">
+        <f>A75</f>
+        <v>73</v>
+      </c>
+      <c r="E12" s="41">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F12" s="7">
         <v>-1</v>
@@ -1977,7 +1990,7 @@
         <v>-1</v>
       </c>
       <c r="H12" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="18">
         <v>-1</v>
@@ -1985,15 +1998,15 @@
       <c r="J12" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L12" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">"Equalizer", </v>
+        <f t="shared" ref="L12:L17" si="7">CONCATENATE("""",B12,""", ")</f>
+        <v xml:space="preserve">"Upper ADSR", </v>
       </c>
       <c r="M12" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="M12:M17" si="8">IF(K12="NULL",CONCATENATE(K12,", "),CONCATENATE("&amp;",K12,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N12" s="11" t="str">
@@ -2002,7 +2015,7 @@
       </c>
       <c r="O12" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Equalizer", 164, 174, -1, NULL, tm_none, -1, -1, 0},  // Idx 10</v>
+        <v xml:space="preserve">  {"Upper ADSR", 45, 73, -1, NULL, tm_none, -1, -1, 1},  // Idx 10</v>
       </c>
       <c r="P12" s="6"/>
     </row>
@@ -2011,20 +2024,20 @@
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="B13" s="30" t="s">
-        <v>87</v>
+      <c r="B13" s="29" t="s">
+        <v>195</v>
       </c>
       <c r="C13" s="17">
-        <f>A47</f>
-        <v>45</v>
+        <f>A40</f>
+        <v>38</v>
       </c>
       <c r="D13" s="17">
-        <f>A75</f>
-        <v>73</v>
-      </c>
-      <c r="E13" s="43">
+        <f>A46</f>
+        <v>44</v>
+      </c>
+      <c r="E13" s="41">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="F13" s="7">
         <v>-1</v>
@@ -2033,7 +2046,7 @@
         <v>-1</v>
       </c>
       <c r="H13" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="18">
         <v>-1</v>
@@ -2045,11 +2058,11 @@
         <v>8</v>
       </c>
       <c r="L13" s="11" t="str">
-        <f t="shared" ref="L13:L18" si="7">CONCATENATE("""",B13,""", ")</f>
-        <v xml:space="preserve">"Upper ADSR", </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">"Upper GM", </v>
       </c>
       <c r="M13" s="11" t="str">
-        <f t="shared" ref="M13:M18" si="8">IF(K13="NULL",CONCATENATE(K13,", "),CONCATENATE("&amp;",K13,", "))</f>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N13" s="11" t="str">
@@ -2058,7 +2071,7 @@
       </c>
       <c r="O13" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Upper ADSR", 45, 73, -1, NULL, tm_none, -1, -1, 1},  // Idx 11</v>
+        <v xml:space="preserve">  {"Upper GM", 38, 44, -1, NULL, tm_none, -1, -1, 0},  // Idx 11</v>
       </c>
       <c r="P13" s="6"/>
     </row>
@@ -2067,20 +2080,20 @@
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="B14" s="30" t="s">
-        <v>84</v>
+      <c r="B14" s="9" t="s">
+        <v>83</v>
       </c>
       <c r="C14" s="17">
-        <f>A40</f>
-        <v>38</v>
+        <f>A95</f>
+        <v>93</v>
       </c>
       <c r="D14" s="17">
-        <f>A46</f>
-        <v>44</v>
-      </c>
-      <c r="E14" s="43">
+        <f>A111</f>
+        <v>109</v>
+      </c>
+      <c r="E14" s="41">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F14" s="7">
         <v>-1</v>
@@ -2089,7 +2102,7 @@
         <v>-1</v>
       </c>
       <c r="H14" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="18">
         <v>-1</v>
@@ -2102,7 +2115,7 @@
       </c>
       <c r="L14" s="11" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">"Upper GM Synth", </v>
+        <v xml:space="preserve">"Lower ADSR", </v>
       </c>
       <c r="M14" s="11" t="str">
         <f t="shared" si="8"/>
@@ -2114,7 +2127,7 @@
       </c>
       <c r="O14" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Upper GM Synth", 38, 44, -1, NULL, tm_none, -1, -1, 0},  // Idx 12</v>
+        <v xml:space="preserve">  {"Lower ADSR", 93, 109, -1, NULL, tm_none, -1, -1, 1},  // Idx 12</v>
       </c>
       <c r="P14" s="6"/>
     </row>
@@ -2124,19 +2137,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>88</v>
+        <v>193</v>
       </c>
       <c r="C15" s="17">
-        <f>A95</f>
-        <v>93</v>
+        <f>A88</f>
+        <v>86</v>
       </c>
       <c r="D15" s="17">
-        <f>A111</f>
-        <v>109</v>
-      </c>
-      <c r="E15" s="43">
+        <f>A94</f>
+        <v>92</v>
+      </c>
+      <c r="E15" s="41">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F15" s="7">
         <v>-1</v>
@@ -2145,7 +2158,7 @@
         <v>-1</v>
       </c>
       <c r="H15" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="18">
         <v>-1</v>
@@ -2158,7 +2171,7 @@
       </c>
       <c r="L15" s="11" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">"Lower ADSR", </v>
+        <v xml:space="preserve">"Lower GM", </v>
       </c>
       <c r="M15" s="11" t="str">
         <f t="shared" si="8"/>
@@ -2170,7 +2183,7 @@
       </c>
       <c r="O15" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Lower ADSR", 93, 109, -1, NULL, tm_none, -1, -1, 1},  // Idx 13</v>
+        <v xml:space="preserve">  {"Lower GM", 86, 92, -1, NULL, tm_none, -1, -1, 0},  // Idx 13</v>
       </c>
       <c r="P15" s="6"/>
     </row>
@@ -2179,20 +2192,20 @@
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>85</v>
+      <c r="B16" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="C16" s="17">
-        <f>A88</f>
-        <v>86</v>
+        <f>A124</f>
+        <v>122</v>
       </c>
       <c r="D16" s="17">
-        <f>A94</f>
-        <v>92</v>
-      </c>
-      <c r="E16" s="43">
+        <f>A128</f>
+        <v>126</v>
+      </c>
+      <c r="E16" s="41">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F16" s="7">
         <v>-1</v>
@@ -2214,7 +2227,7 @@
       </c>
       <c r="L16" s="11" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">"Lower GM Synth", </v>
+        <v xml:space="preserve">"Pedal ADSR", </v>
       </c>
       <c r="M16" s="11" t="str">
         <f t="shared" si="8"/>
@@ -2226,7 +2239,7 @@
       </c>
       <c r="O16" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Lower GM Synth", 86, 92, -1, NULL, tm_none, -1, -1, 0},  // Idx 14</v>
+        <v xml:space="preserve">  {"Pedal ADSR", 122, 126, -1, NULL, tm_none, -1, -1, 0},  // Idx 14</v>
       </c>
       <c r="P16" s="6"/>
     </row>
@@ -2235,20 +2248,20 @@
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="B17" s="28" t="s">
-        <v>118</v>
+      <c r="B17" s="27" t="s">
+        <v>194</v>
       </c>
       <c r="C17" s="17">
-        <f>A124</f>
-        <v>122</v>
+        <f>A117</f>
+        <v>115</v>
       </c>
       <c r="D17" s="17">
-        <f>A128</f>
-        <v>126</v>
-      </c>
-      <c r="E17" s="43">
+        <f>A123</f>
+        <v>121</v>
+      </c>
+      <c r="E17" s="41">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F17" s="7">
         <v>-1</v>
@@ -2270,7 +2283,7 @@
       </c>
       <c r="L17" s="11" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">"Pedal ADSR", </v>
+        <v xml:space="preserve">"Pedal GM", </v>
       </c>
       <c r="M17" s="11" t="str">
         <f t="shared" si="8"/>
@@ -2282,85 +2295,84 @@
       </c>
       <c r="O17" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Pedal ADSR", 122, 126, -1, NULL, tm_none, -1, -1, 0},  // Idx 15</v>
+        <v xml:space="preserve">  {"Pedal GM", 115, 121, -1, NULL, tm_none, -1, -1, 0},  // Idx 15</v>
       </c>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" s="17">
-        <f>A117</f>
-        <v>115</v>
-      </c>
-      <c r="D18" s="17">
-        <f>A123</f>
-        <v>121</v>
-      </c>
-      <c r="E18" s="43">
-        <f t="shared" si="6"/>
-        <v>7</v>
+      <c r="B18" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" s="13">
+        <f>A141</f>
+        <v>139</v>
+      </c>
+      <c r="D18" s="13">
+        <f>A162</f>
+        <v>160</v>
+      </c>
+      <c r="E18" s="41">
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="F18" s="7">
-        <v>-1</v>
-      </c>
-      <c r="G18" s="18">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="G18" s="12">
+        <v>15</v>
       </c>
       <c r="H18" s="7">
         <v>0</v>
       </c>
-      <c r="I18" s="18">
-        <v>-1</v>
-      </c>
-      <c r="J18" s="18" t="s">
-        <v>24</v>
+      <c r="I18" s="12">
+        <v>265</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>144</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>8</v>
+        <v>170</v>
       </c>
       <c r="L18" s="11" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">"Pedal GM Synth", </v>
+        <f t="shared" ref="L18:L26" si="9">CONCATENATE("""",B18,""", ")</f>
+        <v xml:space="preserve">"Organ", </v>
       </c>
       <c r="M18" s="11" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">NULL, </v>
+        <f t="shared" ref="M18:M26" si="10">IF(K18="NULL",CONCATENATE(K18,", "),CONCATENATE("&amp;",K18,", "))</f>
+        <v xml:space="preserve">&amp;saveOrgan, </v>
       </c>
       <c r="N18" s="11" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">tm_none, </v>
+        <v xml:space="preserve">tm_organ, </v>
       </c>
       <c r="O18" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Pedal GM Synth", 115, 121, -1, NULL, tm_none, -1, -1, 0},  // Idx 16</v>
-      </c>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">  {"Organ", 139, 160, 265, &amp;saveOrgan, tm_organ, 0, 15, 0},  // Idx 16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="B19" s="32" t="s">
-        <v>181</v>
+      <c r="B19" s="30" t="s">
+        <v>176</v>
       </c>
       <c r="C19" s="13">
-        <f>A141</f>
-        <v>139</v>
+        <f>A177</f>
+        <v>175</v>
       </c>
       <c r="D19" s="13">
-        <f>A162</f>
-        <v>160</v>
-      </c>
-      <c r="E19" s="43">
+        <f>A189</f>
+        <v>187</v>
+      </c>
+      <c r="E19" s="41">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F19" s="7">
         <v>0</v>
@@ -2372,84 +2384,85 @@
         <v>0</v>
       </c>
       <c r="I19" s="12">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L19" s="11" t="str">
-        <f t="shared" ref="L19:L26" si="9">CONCATENATE("""",B19,""", ")</f>
-        <v xml:space="preserve">"Organ", </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">"Speaker", </v>
       </c>
       <c r="M19" s="11" t="str">
-        <f t="shared" ref="M19:M26" si="10">IF(K19="NULL",CONCATENATE(K19,", "),CONCATENATE("&amp;",K19,", "))</f>
-        <v xml:space="preserve">&amp;saveOrgan, </v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">&amp;saveSpeaker, </v>
       </c>
       <c r="N19" s="11" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">tm_organ, </v>
+        <v xml:space="preserve">tm_speaker, </v>
       </c>
       <c r="O19" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Organ", 139, 160, 265, &amp;saveOrgan, tm_organ, 0, 15, 0},  // Idx 17</v>
-      </c>
+        <v xml:space="preserve">  {"Speaker", 175, 187, 266, &amp;saveSpeaker, tm_speaker, 0, 15, 0},  // Idx 17</v>
+      </c>
+      <c r="P19" s="6"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="B20" s="31" t="s">
-        <v>182</v>
+      <c r="B20" s="33" t="s">
+        <v>185</v>
       </c>
       <c r="C20" s="13">
-        <f>A177</f>
-        <v>175</v>
+        <f>A190</f>
+        <v>188</v>
       </c>
       <c r="D20" s="13">
-        <f>A189</f>
-        <v>187</v>
-      </c>
-      <c r="E20" s="43">
+        <f>A201</f>
+        <v>199</v>
+      </c>
+      <c r="E20" s="41">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20" s="7">
-        <v>0</v>
-      </c>
-      <c r="G20" s="12">
-        <v>15</v>
+        <v>-1</v>
+      </c>
+      <c r="G20" s="18">
+        <v>-1</v>
       </c>
       <c r="H20" s="7">
         <v>0</v>
       </c>
-      <c r="I20" s="12">
-        <v>266</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>148</v>
+      <c r="I20" s="18">
+        <v>-1</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="L20" s="11" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">"Speaker", </v>
+        <v xml:space="preserve">"Keybd Setup", </v>
       </c>
       <c r="M20" s="11" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">&amp;saveSpeaker, </v>
+        <v xml:space="preserve">&amp;saveDefaults, </v>
       </c>
       <c r="N20" s="11" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">tm_speaker, </v>
+        <v xml:space="preserve">tm_none, </v>
       </c>
       <c r="O20" s="10" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Speaker", 175, 187, 266, &amp;saveSpeaker, tm_speaker, 0, 15, 0},  // Idx 18</v>
+        <v xml:space="preserve">  {"Keybd Setup", 188, 199, -1, &amp;saveDefaults, tm_none, -1, -1, 0},  // Idx 18</v>
       </c>
       <c r="P20" s="6"/>
     </row>
@@ -2458,20 +2471,20 @@
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="B21" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="C21" s="13">
-        <f>A190</f>
-        <v>188</v>
-      </c>
-      <c r="D21" s="13">
-        <f>A201</f>
-        <v>199</v>
-      </c>
-      <c r="E21" s="43">
-        <f t="shared" si="0"/>
-        <v>12</v>
+      <c r="B21" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="C21" s="17">
+        <f>A204</f>
+        <v>202</v>
+      </c>
+      <c r="D21" s="17">
+        <f>A207</f>
+        <v>205</v>
+      </c>
+      <c r="E21" s="41">
+        <f>D21-C21+1</f>
+        <v>4</v>
       </c>
       <c r="F21" s="7">
         <v>-1</v>
@@ -2485,37 +2498,37 @@
       <c r="I21" s="18">
         <v>-1</v>
       </c>
-      <c r="J21" s="18" t="s">
+      <c r="J21" s="7" t="s">
         <v>24</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>177</v>
+        <v>8</v>
       </c>
       <c r="L21" s="11" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">"Keybd Setup", </v>
+        <f>CONCATENATE("""",B21,""", ")</f>
+        <v xml:space="preserve">"Settings", </v>
       </c>
       <c r="M21" s="11" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">&amp;saveDefaults, </v>
+        <f>IF(K21="NULL",CONCATENATE(K21,", "),CONCATENATE("&amp;",K21,", "))</f>
+        <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N21" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(J21="NULL",CONCATENATE(J21,", "),CONCATENATE("tm_",J21,", "))</f>
         <v xml:space="preserve">tm_none, </v>
       </c>
       <c r="O21" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">  {"Keybd Setup", 188, 199, -1, &amp;saveDefaults, tm_none, -1, -1, 0},  // Idx 19</v>
+        <f>CONCATENATE("  {",L21,C21,", ",D21,", ",I21,", ",M21,N21,F21,", ",G21,", ",H21,"},  // Idx ", A21)</f>
+        <v xml:space="preserve">  {"Settings", 202, 205, -1, NULL, tm_none, -1, -1, 0},  // Idx 19</v>
       </c>
       <c r="P21" s="6"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
-        <f t="shared" si="5"/>
+        <f>A21+1</f>
         <v>20</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C22" s="13">
         <v>-1</v>
@@ -2537,7 +2550,7 @@
         <v>87</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>8</v>
@@ -2562,11 +2575,11 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="A23" si="11">A22+1</f>
         <v>21</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C23" s="13">
         <v>-1</v>
@@ -2588,7 +2601,7 @@
         <v>88</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>8</v>
@@ -2613,11 +2626,11 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
-        <f t="shared" ref="A5:A63" si="11">A23+1</f>
+        <f t="shared" ref="A24:A63" si="12">A23+1</f>
         <v>22</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C24" s="13">
         <v>-1</v>
@@ -2663,11 +2676,11 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C25" s="13">
         <v>-1</v>
@@ -2713,11 +2726,11 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C26" s="13">
         <v>-1</v>
@@ -2764,11 +2777,11 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>25</v>
       </c>
-      <c r="B27" s="45" t="s">
-        <v>183</v>
+      <c r="B27" s="43" t="s">
+        <v>177</v>
       </c>
       <c r="C27" s="13">
         <v>-1</v>
@@ -2776,7 +2789,7 @@
       <c r="D27" s="13">
         <v>-1</v>
       </c>
-      <c r="E27" s="43"/>
+      <c r="E27" s="41"/>
       <c r="F27" s="3">
         <v>0</v>
       </c>
@@ -2796,11 +2809,11 @@
         <v>8</v>
       </c>
       <c r="L27" s="11" t="str">
-        <f t="shared" ref="L27" si="12">CONCATENATE("""",B27,""", ")</f>
+        <f t="shared" ref="L27" si="13">CONCATENATE("""",B27,""", ")</f>
         <v xml:space="preserve">"Amp Bypass", </v>
       </c>
       <c r="M27" s="11" t="str">
-        <f t="shared" ref="M27" si="13">IF(K27="NULL",CONCATENATE(K27,", "),CONCATENATE("&amp;",K27,", "))</f>
+        <f t="shared" ref="M27" si="14">IF(K27="NULL",CONCATENATE(K27,", "),CONCATENATE("&amp;",K27,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N27" s="11" t="str">
@@ -2815,11 +2828,11 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>26</v>
       </c>
-      <c r="B28" s="30" t="s">
-        <v>67</v>
+      <c r="B28" s="29" t="s">
+        <v>65</v>
       </c>
       <c r="C28" s="13">
         <v>-1</v>
@@ -2847,11 +2860,11 @@
         <v>8</v>
       </c>
       <c r="L28" s="11" t="str">
-        <f t="shared" ref="L28:L36" si="14">CONCATENATE("""",B28,""", ")</f>
+        <f t="shared" ref="L28:L36" si="15">CONCATENATE("""",B28,""", ")</f>
         <v xml:space="preserve">"Drawbar 16", </v>
       </c>
       <c r="M28" s="11" t="str">
-        <f t="shared" ref="M28:M36" si="15">IF(K28="NULL",CONCATENATE(K28,", "),CONCATENATE("&amp;",K28,", "))</f>
+        <f t="shared" ref="M28:M36" si="16">IF(K28="NULL",CONCATENATE(K28,", "),CONCATENATE("&amp;",K28,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N28" s="11" t="str">
@@ -2866,11 +2879,11 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>27</v>
       </c>
-      <c r="B29" s="30" t="s">
-        <v>68</v>
+      <c r="B29" s="29" t="s">
+        <v>66</v>
       </c>
       <c r="C29" s="13">
         <v>-1</v>
@@ -2898,11 +2911,11 @@
         <v>8</v>
       </c>
       <c r="L29" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">"Drawbar 5 1/3", </v>
       </c>
       <c r="M29" s="11" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N29" s="11" t="str">
@@ -2917,11 +2930,11 @@
     </row>
     <row r="30" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>28</v>
       </c>
-      <c r="B30" s="30" t="s">
-        <v>69</v>
+      <c r="B30" s="29" t="s">
+        <v>67</v>
       </c>
       <c r="C30" s="13">
         <v>-1</v>
@@ -2949,11 +2962,11 @@
         <v>8</v>
       </c>
       <c r="L30" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">"Drawbar 8", </v>
       </c>
       <c r="M30" s="11" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N30" s="11" t="str">
@@ -2967,11 +2980,11 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>29</v>
       </c>
-      <c r="B31" s="30" t="s">
-        <v>70</v>
+      <c r="B31" s="29" t="s">
+        <v>68</v>
       </c>
       <c r="C31" s="13">
         <v>-1</v>
@@ -2999,11 +3012,11 @@
         <v>8</v>
       </c>
       <c r="L31" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">"Drawbar 4", </v>
       </c>
       <c r="M31" s="11" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N31" s="11" t="str">
@@ -3017,11 +3030,11 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
-      <c r="B32" s="30" t="s">
-        <v>71</v>
+      <c r="B32" s="29" t="s">
+        <v>69</v>
       </c>
       <c r="C32" s="13">
         <v>-1</v>
@@ -3049,11 +3062,11 @@
         <v>8</v>
       </c>
       <c r="L32" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">"Drawbar 2 2/3", </v>
       </c>
       <c r="M32" s="11" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N32" s="11" t="str">
@@ -3067,11 +3080,11 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
-      <c r="B33" s="30" t="s">
-        <v>72</v>
+      <c r="B33" s="29" t="s">
+        <v>70</v>
       </c>
       <c r="C33" s="13">
         <v>-1</v>
@@ -3099,11 +3112,11 @@
         <v>8</v>
       </c>
       <c r="L33" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">"Drawbar 2", </v>
       </c>
       <c r="M33" s="11" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N33" s="11" t="str">
@@ -3117,11 +3130,11 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>32</v>
       </c>
-      <c r="B34" s="30" t="s">
-        <v>73</v>
+      <c r="B34" s="29" t="s">
+        <v>71</v>
       </c>
       <c r="C34" s="13">
         <v>-1</v>
@@ -3149,11 +3162,11 @@
         <v>8</v>
       </c>
       <c r="L34" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">"Drawbar 1 3/5", </v>
       </c>
       <c r="M34" s="11" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N34" s="11" t="str">
@@ -3167,11 +3180,11 @@
     </row>
     <row r="35" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>33</v>
       </c>
-      <c r="B35" s="30" t="s">
-        <v>74</v>
+      <c r="B35" s="29" t="s">
+        <v>72</v>
       </c>
       <c r="C35" s="13">
         <v>-1</v>
@@ -3199,29 +3212,29 @@
         <v>8</v>
       </c>
       <c r="L35" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">"Drawbar 1 1/3", </v>
       </c>
       <c r="M35" s="11" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N35" s="11" t="str">
-        <f t="shared" ref="N35:N66" si="16">IF(J35="NULL",CONCATENATE(J35,", "),CONCATENATE("tm_",J35,", "))</f>
+        <f t="shared" ref="N35:N66" si="17">IF(J35="NULL",CONCATENATE(J35,", "),CONCATENATE("tm_",J35,", "))</f>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O35" s="10" t="str">
-        <f t="shared" ref="O35:O66" si="17">CONCATENATE("  {",L35,C35,", ",D35,", ",I35,", ",M35,N35,F35,", ",G35,", ",H35,"},  // Idx ", A35)</f>
+        <f t="shared" ref="O35:O66" si="18">CONCATENATE("  {",L35,C35,", ",D35,", ",I35,", ",M35,N35,F35,", ",G35,", ",H35,"},  // Idx ", A35)</f>
         <v xml:space="preserve">  {"Drawbar 1 1/3", -1, -1, 7, NULL, tm_drawbar, 0, 127, 0},  // Idx 33</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>34</v>
       </c>
-      <c r="B36" s="30" t="s">
-        <v>75</v>
+      <c r="B36" s="29" t="s">
+        <v>73</v>
       </c>
       <c r="C36" s="13">
         <v>-1</v>
@@ -3249,29 +3262,29 @@
         <v>8</v>
       </c>
       <c r="L36" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">"Drawbar 1", </v>
       </c>
       <c r="M36" s="11" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N36" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O36" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Drawbar 1", -1, -1, 8, NULL, tm_drawbar, 0, 127, 0},  // Idx 34</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>35</v>
       </c>
-      <c r="B37" s="30" t="s">
-        <v>76</v>
+      <c r="B37" s="29" t="s">
+        <v>74</v>
       </c>
       <c r="C37" s="13">
         <v>-1</v>
@@ -3299,29 +3312,29 @@
         <v>8</v>
       </c>
       <c r="L37" s="11" t="str">
-        <f t="shared" ref="L37:L94" si="18">CONCATENATE("""",B37,""", ")</f>
+        <f t="shared" ref="L37:L94" si="19">CONCATENATE("""",B37,""", ")</f>
         <v xml:space="preserve">"Drawbar Mix 1", </v>
       </c>
       <c r="M37" s="11" t="str">
-        <f t="shared" ref="M37:M94" si="19">IF(K37="NULL",CONCATENATE(K37,", "),CONCATENATE("&amp;",K37,", "))</f>
+        <f t="shared" ref="M37:M94" si="20">IF(K37="NULL",CONCATENATE(K37,", "),CONCATENATE("&amp;",K37,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N37" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O37" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Drawbar Mix 1", -1, -1, 9, NULL, tm_drawbar, 0, 127, 0},  // Idx 35</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>36</v>
       </c>
-      <c r="B38" s="30" t="s">
-        <v>77</v>
+      <c r="B38" s="29" t="s">
+        <v>75</v>
       </c>
       <c r="C38" s="13">
         <v>-1</v>
@@ -3349,29 +3362,29 @@
         <v>8</v>
       </c>
       <c r="L38" s="11" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">"Drawbar Mix 2", </v>
+      </c>
+      <c r="M38" s="11" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N38" s="11" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">tm_drawbar, </v>
+      </c>
+      <c r="O38" s="10" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">"Drawbar Mix 2", </v>
-      </c>
-      <c r="M38" s="11" t="str">
-        <f t="shared" si="19"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N38" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve">tm_drawbar, </v>
-      </c>
-      <c r="O38" s="10" t="str">
-        <f t="shared" si="17"/>
         <v xml:space="preserve">  {"Drawbar Mix 2", -1, -1, 10, NULL, tm_drawbar, 0, 127, 0},  // Idx 36</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>37</v>
       </c>
-      <c r="B39" s="30" t="s">
-        <v>78</v>
+      <c r="B39" s="29" t="s">
+        <v>76</v>
       </c>
       <c r="C39" s="13">
         <v>-1</v>
@@ -3399,29 +3412,29 @@
         <v>8</v>
       </c>
       <c r="L39" s="11" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">"Drawbar Mix 3", </v>
+      </c>
+      <c r="M39" s="11" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N39" s="11" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">tm_drawbar, </v>
+      </c>
+      <c r="O39" s="10" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">"Drawbar Mix 3", </v>
-      </c>
-      <c r="M39" s="11" t="str">
-        <f t="shared" si="19"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N39" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve">tm_drawbar, </v>
-      </c>
-      <c r="O39" s="10" t="str">
-        <f t="shared" si="17"/>
         <v xml:space="preserve">  {"Drawbar Mix 3", -1, -1, 11, NULL, tm_drawbar, 0, 127, 0},  // Idx 37</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>38</v>
       </c>
-      <c r="B40" s="39" t="s">
-        <v>79</v>
+      <c r="B40" s="37" t="s">
+        <v>77</v>
       </c>
       <c r="C40" s="13">
         <v>-1</v>
@@ -3449,29 +3462,29 @@
         <v>8</v>
       </c>
       <c r="L40" s="11" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">"GM Prg 1", </v>
+      </c>
+      <c r="M40" s="11" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N40" s="11" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">tm_numeric, </v>
+      </c>
+      <c r="O40" s="10" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">"GM Prg 1", </v>
-      </c>
-      <c r="M40" s="11" t="str">
-        <f t="shared" si="19"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N40" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve">tm_numeric, </v>
-      </c>
-      <c r="O40" s="10" t="str">
-        <f t="shared" si="17"/>
         <v xml:space="preserve">  {"GM Prg 1", -1, -1, 224, NULL, tm_numeric, 0, 126, 0},  // Idx 38</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>39</v>
       </c>
-      <c r="B41" s="39" t="s">
-        <v>159</v>
+      <c r="B41" s="37" t="s">
+        <v>154</v>
       </c>
       <c r="C41" s="13">
         <v>-1</v>
@@ -3493,35 +3506,35 @@
         <v>225</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L41" s="11" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">"GM Level 1", </v>
+      </c>
+      <c r="M41" s="11" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N41" s="11" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O41" s="10" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">"GM Level 1", </v>
-      </c>
-      <c r="M41" s="11" t="str">
-        <f t="shared" si="19"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N41" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O41" s="10" t="str">
-        <f t="shared" si="17"/>
         <v xml:space="preserve">  {"GM Level 1", -1, -1, 225, NULL, tm_pot, 0, 127, 0},  // Idx 39</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>40</v>
       </c>
-      <c r="B42" s="39" t="s">
-        <v>80</v>
+      <c r="B42" s="37" t="s">
+        <v>78</v>
       </c>
       <c r="C42" s="13">
         <v>-1</v>
@@ -3549,29 +3562,29 @@
         <v>8</v>
       </c>
       <c r="L42" s="11" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">"GM Hrm 1", </v>
+      </c>
+      <c r="M42" s="11" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N42" s="11" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">tm_numeric, </v>
+      </c>
+      <c r="O42" s="10" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">"GM Hrm 1", </v>
-      </c>
-      <c r="M42" s="11" t="str">
-        <f t="shared" si="19"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N42" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve">tm_numeric, </v>
-      </c>
-      <c r="O42" s="10" t="str">
-        <f t="shared" si="17"/>
         <v xml:space="preserve">  {"GM Hrm 1", -1, -1, 226, NULL, tm_numeric, 0, 5, 0},  // Idx 40</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>41</v>
       </c>
-      <c r="B43" s="39" t="s">
-        <v>81</v>
+      <c r="B43" s="37" t="s">
+        <v>79</v>
       </c>
       <c r="C43" s="13">
         <v>-1</v>
@@ -3599,29 +3612,29 @@
         <v>8</v>
       </c>
       <c r="L43" s="11" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">"GM Prg 2", </v>
+      </c>
+      <c r="M43" s="11" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N43" s="11" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">tm_numeric, </v>
+      </c>
+      <c r="O43" s="10" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">"GM Prg 2", </v>
-      </c>
-      <c r="M43" s="11" t="str">
-        <f t="shared" si="19"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N43" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve">tm_numeric, </v>
-      </c>
-      <c r="O43" s="10" t="str">
-        <f t="shared" si="17"/>
         <v xml:space="preserve">  {"GM Prg 2", -1, -1, 227, NULL, tm_numeric, 0, 126, 1},  // Idx 41</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>42</v>
       </c>
-      <c r="B44" s="39" t="s">
-        <v>160</v>
+      <c r="B44" s="37" t="s">
+        <v>155</v>
       </c>
       <c r="C44" s="13">
         <v>-1</v>
@@ -3643,35 +3656,35 @@
         <v>228</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K44" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L44" s="11" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">"GM Level 2", </v>
+      </c>
+      <c r="M44" s="11" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N44" s="11" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O44" s="10" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">"GM Level 2", </v>
-      </c>
-      <c r="M44" s="11" t="str">
-        <f t="shared" si="19"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N44" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O44" s="10" t="str">
-        <f t="shared" si="17"/>
         <v xml:space="preserve">  {"GM Level 2", -1, -1, 228, NULL, tm_pot, 0, 127, 1},  // Idx 42</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>43</v>
       </c>
-      <c r="B45" s="39" t="s">
-        <v>82</v>
+      <c r="B45" s="37" t="s">
+        <v>80</v>
       </c>
       <c r="C45" s="13">
         <v>-1</v>
@@ -3699,29 +3712,29 @@
         <v>8</v>
       </c>
       <c r="L45" s="11" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">"GM Harm2", </v>
+      </c>
+      <c r="M45" s="11" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N45" s="11" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">tm_numeric, </v>
+      </c>
+      <c r="O45" s="10" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">"GM Harm2", </v>
-      </c>
-      <c r="M45" s="11" t="str">
-        <f t="shared" si="19"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N45" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve">tm_numeric, </v>
-      </c>
-      <c r="O45" s="10" t="str">
-        <f t="shared" si="17"/>
         <v xml:space="preserve">  {"GM Harm2", -1, -1, 229, NULL, tm_numeric, 0, 5, 1},  // Idx 43</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>44</v>
       </c>
-      <c r="B46" s="39" t="s">
-        <v>119</v>
+      <c r="B46" s="37" t="s">
+        <v>114</v>
       </c>
       <c r="C46" s="13">
         <v>-1</v>
@@ -3743,35 +3756,35 @@
         <v>230</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K46" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L46" s="11" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">"GM Detune 2", </v>
+      </c>
+      <c r="M46" s="11" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N46" s="11" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O46" s="10" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">"GM Detune 2", </v>
-      </c>
-      <c r="M46" s="11" t="str">
-        <f t="shared" si="19"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N46" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O46" s="10" t="str">
-        <f t="shared" si="17"/>
         <v xml:space="preserve">  {"GM Detune 2", -1, -1, 230, NULL, tm_pot, 0, 15, 1},  // Idx 44</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>45</v>
       </c>
-      <c r="B47" s="40" t="s">
-        <v>89</v>
+      <c r="B47" s="38" t="s">
+        <v>84</v>
       </c>
       <c r="C47" s="13">
         <v>-1</v>
@@ -3799,29 +3812,29 @@
         <v>8</v>
       </c>
       <c r="L47" s="11" t="str">
-        <f t="shared" ref="L47:L75" si="20">CONCATENATE("""",B47,""", ")</f>
+        <f t="shared" ref="L47:L75" si="21">CONCATENATE("""",B47,""", ")</f>
         <v xml:space="preserve">"Env/Perc 16", </v>
       </c>
       <c r="M47" s="11" t="str">
-        <f t="shared" ref="M47:M75" si="21">IF(K47="NULL",CONCATENATE(K47,", "),CONCATENATE("&amp;",K47,", "))</f>
+        <f t="shared" ref="M47:M75" si="22">IF(K47="NULL",CONCATENATE(K47,", "),CONCATENATE("&amp;",K47,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N47" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O47" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Env/Perc 16", -1, -1, 96, NULL, tm_drawbar, 0, 127, 1},  // Idx 45</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>46</v>
       </c>
-      <c r="B48" s="40" t="s">
-        <v>90</v>
+      <c r="B48" s="38" t="s">
+        <v>85</v>
       </c>
       <c r="C48" s="13">
         <v>-1</v>
@@ -3849,29 +3862,29 @@
         <v>8</v>
       </c>
       <c r="L48" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Env/Perc 5 1/3", </v>
       </c>
       <c r="M48" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N48" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O48" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Env/Perc 5 1/3", -1, -1, 97, NULL, tm_drawbar, 0, 127, 1},  // Idx 46</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>47</v>
       </c>
-      <c r="B49" s="40" t="s">
-        <v>91</v>
+      <c r="B49" s="38" t="s">
+        <v>86</v>
       </c>
       <c r="C49" s="13">
         <v>-1</v>
@@ -3899,29 +3912,29 @@
         <v>8</v>
       </c>
       <c r="L49" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Env/Perc 8", </v>
       </c>
       <c r="M49" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N49" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O49" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Env/Perc 8", -1, -1, 98, NULL, tm_drawbar, 0, 127, 1},  // Idx 47</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>48</v>
       </c>
-      <c r="B50" s="40" t="s">
-        <v>92</v>
+      <c r="B50" s="38" t="s">
+        <v>87</v>
       </c>
       <c r="C50" s="13">
         <v>-1</v>
@@ -3949,29 +3962,29 @@
         <v>8</v>
       </c>
       <c r="L50" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Env/Perc 4", </v>
       </c>
       <c r="M50" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N50" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O50" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Env/Perc 4", -1, -1, 99, NULL, tm_drawbar, 0, 127, 1},  // Idx 48</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>49</v>
       </c>
-      <c r="B51" s="40" t="s">
-        <v>93</v>
+      <c r="B51" s="38" t="s">
+        <v>88</v>
       </c>
       <c r="C51" s="13">
         <v>-1</v>
@@ -3999,29 +4012,29 @@
         <v>8</v>
       </c>
       <c r="L51" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Env/Perc 2 2/3", </v>
       </c>
       <c r="M51" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N51" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O51" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Env/Perc 2 2/3", -1, -1, 100, NULL, tm_drawbar, 0, 127, 1},  // Idx 49</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>50</v>
       </c>
-      <c r="B52" s="40" t="s">
-        <v>94</v>
+      <c r="B52" s="38" t="s">
+        <v>89</v>
       </c>
       <c r="C52" s="13">
         <v>-1</v>
@@ -4049,29 +4062,29 @@
         <v>8</v>
       </c>
       <c r="L52" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Env/Perc 2", </v>
       </c>
       <c r="M52" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N52" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O52" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Env/Perc 2", -1, -1, 101, NULL, tm_drawbar, 0, 127, 1},  // Idx 50</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>51</v>
       </c>
-      <c r="B53" s="40" t="s">
-        <v>95</v>
+      <c r="B53" s="38" t="s">
+        <v>90</v>
       </c>
       <c r="C53" s="13">
         <v>-1</v>
@@ -4099,29 +4112,29 @@
         <v>8</v>
       </c>
       <c r="L53" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Env/Perc 1 3/5", </v>
       </c>
       <c r="M53" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N53" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O53" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Env/Perc 1 3/5", -1, -1, 102, NULL, tm_drawbar, 0, 127, 1},  // Idx 51</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>52</v>
       </c>
-      <c r="B54" s="40" t="s">
-        <v>96</v>
+      <c r="B54" s="38" t="s">
+        <v>91</v>
       </c>
       <c r="C54" s="13">
         <v>-1</v>
@@ -4149,29 +4162,29 @@
         <v>8</v>
       </c>
       <c r="L54" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Env/Perc 1 1/3", </v>
       </c>
       <c r="M54" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N54" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O54" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Env/Perc 1 1/3", -1, -1, 103, NULL, tm_drawbar, 0, 127, 1},  // Idx 52</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>53</v>
       </c>
-      <c r="B55" s="40" t="s">
-        <v>97</v>
+      <c r="B55" s="38" t="s">
+        <v>92</v>
       </c>
       <c r="C55" s="13">
         <v>-1</v>
@@ -4199,29 +4212,29 @@
         <v>8</v>
       </c>
       <c r="L55" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Env/Perc 1", </v>
       </c>
       <c r="M55" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N55" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O55" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Env/Perc 1", -1, -1, 104, NULL, tm_drawbar, 0, 127, 1},  // Idx 53</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>54</v>
       </c>
-      <c r="B56" s="40" t="s">
-        <v>112</v>
+      <c r="B56" s="38" t="s">
+        <v>107</v>
       </c>
       <c r="C56" s="13">
         <v>-1</v>
@@ -4249,29 +4262,29 @@
         <v>8</v>
       </c>
       <c r="L56" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Env/Perc Mix 1", </v>
       </c>
       <c r="M56" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N56" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O56" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Env/Perc Mix 1", -1, -1, 105, NULL, tm_drawbar, 0, 127, 1},  // Idx 54</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>55</v>
       </c>
-      <c r="B57" s="40" t="s">
-        <v>113</v>
+      <c r="B57" s="38" t="s">
+        <v>108</v>
       </c>
       <c r="C57" s="13">
         <v>-1</v>
@@ -4299,29 +4312,29 @@
         <v>8</v>
       </c>
       <c r="L57" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Env/Perc Mix 2", </v>
       </c>
       <c r="M57" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N57" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O57" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Env/Perc Mix 2", -1, -1, 106, NULL, tm_drawbar, 0, 127, 1},  // Idx 55</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>56</v>
       </c>
-      <c r="B58" s="40" t="s">
-        <v>114</v>
+      <c r="B58" s="38" t="s">
+        <v>109</v>
       </c>
       <c r="C58" s="13">
         <v>-1</v>
@@ -4349,29 +4362,29 @@
         <v>8</v>
       </c>
       <c r="L58" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Env/Perc Mix 3", </v>
       </c>
       <c r="M58" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N58" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O58" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Env/Perc Mix 3", -1, -1, 107, NULL, tm_drawbar, 0, 127, 1},  // Idx 56</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>57</v>
       </c>
-      <c r="B59" s="40" t="s">
-        <v>107</v>
+      <c r="B59" s="38" t="s">
+        <v>102</v>
       </c>
       <c r="C59" s="13">
         <v>-1</v>
@@ -4393,35 +4406,35 @@
         <v>107</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K59" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L59" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Attack", </v>
       </c>
       <c r="M59" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N59" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O59" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Attack", -1, -1, 107, NULL, tm_pot, 0, 127, 1},  // Idx 57</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>58</v>
       </c>
-      <c r="B60" s="40" t="s">
-        <v>108</v>
+      <c r="B60" s="38" t="s">
+        <v>103</v>
       </c>
       <c r="C60" s="13">
         <v>-1</v>
@@ -4443,35 +4456,35 @@
         <v>107</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K60" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L60" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Decay", </v>
       </c>
       <c r="M60" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N60" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O60" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Decay", -1, -1, 107, NULL, tm_pot, 0, 127, 1},  // Idx 58</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>59</v>
       </c>
-      <c r="B61" s="40" t="s">
-        <v>109</v>
+      <c r="B61" s="38" t="s">
+        <v>104</v>
       </c>
       <c r="C61" s="13">
         <v>-1</v>
@@ -4493,35 +4506,35 @@
         <v>107</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K61" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L61" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Sustain", </v>
       </c>
       <c r="M61" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N61" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O61" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Sustain", -1, -1, 107, NULL, tm_pot, 0, 127, 1},  // Idx 59</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>60</v>
       </c>
-      <c r="B62" s="40" t="s">
-        <v>110</v>
+      <c r="B62" s="38" t="s">
+        <v>105</v>
       </c>
       <c r="C62" s="13">
         <v>-1</v>
@@ -4543,35 +4556,35 @@
         <v>107</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K62" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L62" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"Release", </v>
       </c>
       <c r="M62" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N62" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O62" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"Release", -1, -1, 107, NULL, tm_pot, 0, 127, 1},  // Idx 60</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>61</v>
       </c>
-      <c r="B63" s="40" t="s">
-        <v>111</v>
+      <c r="B63" s="38" t="s">
+        <v>106</v>
       </c>
       <c r="C63" s="13">
         <v>-1</v>
@@ -4593,35 +4606,35 @@
         <v>107</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K63" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L63" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"ADSR Harmonic", </v>
       </c>
       <c r="M63" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N63" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O63" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"ADSR Harmonic", -1, -1, 107, NULL, tm_pot, 0, 127, 1},  // Idx 61</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="16">
-        <f t="shared" ref="A64:A125" si="22">A63+1</f>
+        <f t="shared" ref="A64:A125" si="23">A63+1</f>
         <v>62</v>
       </c>
-      <c r="B64" s="40" t="s">
-        <v>98</v>
+      <c r="B64" s="38" t="s">
+        <v>93</v>
       </c>
       <c r="C64" s="13">
         <v>-1</v>
@@ -4649,29 +4662,29 @@
         <v>8</v>
       </c>
       <c r="L64" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"ADSR on 16", </v>
       </c>
       <c r="M64" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N64" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O64" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"ADSR on 16", -1, -1, 160, NULL, tm_tab, 0, 1, 1},  // Idx 62</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>63</v>
       </c>
-      <c r="B65" s="40" t="s">
-        <v>99</v>
+      <c r="B65" s="38" t="s">
+        <v>94</v>
       </c>
       <c r="C65" s="13">
         <v>-1</v>
@@ -4699,29 +4712,29 @@
         <v>8</v>
       </c>
       <c r="L65" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"ADSR on 5 1/3", </v>
       </c>
       <c r="M65" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N65" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O65" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"ADSR on 5 1/3", -1, -1, 161, NULL, tm_tab, 0, 1, 1},  // Idx 63</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>64</v>
       </c>
-      <c r="B66" s="40" t="s">
-        <v>100</v>
+      <c r="B66" s="38" t="s">
+        <v>95</v>
       </c>
       <c r="C66" s="13">
         <v>-1</v>
@@ -4749,29 +4762,29 @@
         <v>8</v>
       </c>
       <c r="L66" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"ADSR on 8", </v>
       </c>
       <c r="M66" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N66" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O66" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {"ADSR on 8", -1, -1, 162, NULL, tm_tab, 0, 1, 1},  // Idx 64</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>65</v>
       </c>
-      <c r="B67" s="40" t="s">
-        <v>101</v>
+      <c r="B67" s="38" t="s">
+        <v>96</v>
       </c>
       <c r="C67" s="13">
         <v>-1</v>
@@ -4799,29 +4812,29 @@
         <v>8</v>
       </c>
       <c r="L67" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"ADSR on 4", </v>
       </c>
       <c r="M67" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N67" s="11" t="str">
-        <f t="shared" ref="N67:N98" si="23">IF(J67="NULL",CONCATENATE(J67,", "),CONCATENATE("tm_",J67,", "))</f>
+        <f t="shared" ref="N67:N98" si="24">IF(J67="NULL",CONCATENATE(J67,", "),CONCATENATE("tm_",J67,", "))</f>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O67" s="10" t="str">
-        <f t="shared" ref="O67:O98" si="24">CONCATENATE("  {",L67,C67,", ",D67,", ",I67,", ",M67,N67,F67,", ",G67,", ",H67,"},  // Idx ", A67)</f>
+        <f t="shared" ref="O67:O98" si="25">CONCATENATE("  {",L67,C67,", ",D67,", ",I67,", ",M67,N67,F67,", ",G67,", ",H67,"},  // Idx ", A67)</f>
         <v xml:space="preserve">  {"ADSR on 4", -1, -1, 163, NULL, tm_tab, 0, 1, 1},  // Idx 65</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>66</v>
       </c>
-      <c r="B68" s="40" t="s">
-        <v>102</v>
+      <c r="B68" s="38" t="s">
+        <v>97</v>
       </c>
       <c r="C68" s="13">
         <v>-1</v>
@@ -4849,29 +4862,29 @@
         <v>8</v>
       </c>
       <c r="L68" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"ADSR on 2 2/3", </v>
       </c>
       <c r="M68" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N68" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O68" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"ADSR on 2 2/3", -1, -1, 164, NULL, tm_tab, 0, 1, 1},  // Idx 66</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>67</v>
       </c>
-      <c r="B69" s="40" t="s">
-        <v>103</v>
+      <c r="B69" s="38" t="s">
+        <v>98</v>
       </c>
       <c r="C69" s="13">
         <v>-1</v>
@@ -4899,29 +4912,29 @@
         <v>8</v>
       </c>
       <c r="L69" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"ADSR on 2", </v>
       </c>
       <c r="M69" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N69" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O69" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"ADSR on 2", -1, -1, 165, NULL, tm_tab, 0, 1, 1},  // Idx 67</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>68</v>
       </c>
-      <c r="B70" s="40" t="s">
-        <v>104</v>
+      <c r="B70" s="38" t="s">
+        <v>99</v>
       </c>
       <c r="C70" s="13">
         <v>-1</v>
@@ -4949,29 +4962,29 @@
         <v>8</v>
       </c>
       <c r="L70" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"ADSR on 1 3/5", </v>
       </c>
       <c r="M70" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N70" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O70" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"ADSR on 1 3/5", -1, -1, 166, NULL, tm_tab, 0, 1, 1},  // Idx 68</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>69</v>
       </c>
-      <c r="B71" s="40" t="s">
-        <v>105</v>
+      <c r="B71" s="38" t="s">
+        <v>100</v>
       </c>
       <c r="C71" s="13">
         <v>-1</v>
@@ -4999,29 +5012,29 @@
         <v>8</v>
       </c>
       <c r="L71" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"ADSR on 1 1/3", </v>
       </c>
       <c r="M71" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N71" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O71" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"ADSR on 1 1/3", -1, -1, 167, NULL, tm_tab, 0, 1, 1},  // Idx 69</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>70</v>
       </c>
-      <c r="B72" s="40" t="s">
-        <v>106</v>
+      <c r="B72" s="38" t="s">
+        <v>101</v>
       </c>
       <c r="C72" s="13">
         <v>-1</v>
@@ -5049,29 +5062,29 @@
         <v>8</v>
       </c>
       <c r="L72" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"ADSR on 1", </v>
       </c>
       <c r="M72" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N72" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O72" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"ADSR on 1", -1, -1, 168, NULL, tm_tab, 0, 1, 1},  // Idx 70</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>71</v>
       </c>
-      <c r="B73" s="40" t="s">
-        <v>115</v>
+      <c r="B73" s="38" t="s">
+        <v>110</v>
       </c>
       <c r="C73" s="13">
         <v>-1</v>
@@ -5099,29 +5112,29 @@
         <v>8</v>
       </c>
       <c r="L73" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"ADSR on Mix 1", </v>
       </c>
       <c r="M73" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N73" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O73" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"ADSR on Mix 1", -1, -1, 169, NULL, tm_tab, 0, 1, 1},  // Idx 71</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>72</v>
       </c>
-      <c r="B74" s="40" t="s">
-        <v>116</v>
+      <c r="B74" s="38" t="s">
+        <v>111</v>
       </c>
       <c r="C74" s="13">
         <v>-1</v>
@@ -5149,29 +5162,29 @@
         <v>8</v>
       </c>
       <c r="L74" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"ADSR on Mix 2", </v>
       </c>
       <c r="M74" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N74" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O74" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"ADSR on Mix 2", -1, -1, 170, NULL, tm_tab, 0, 1, 1},  // Idx 72</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>73</v>
       </c>
-      <c r="B75" s="40" t="s">
-        <v>117</v>
+      <c r="B75" s="38" t="s">
+        <v>112</v>
       </c>
       <c r="C75" s="13">
         <v>-1</v>
@@ -5199,29 +5212,29 @@
         <v>8</v>
       </c>
       <c r="L75" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">"ADSR on Mix 3", </v>
       </c>
       <c r="M75" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N75" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O75" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"ADSR on Mix 3", -1, -1, 171, NULL, tm_tab, 0, 1, 1},  // Idx 73</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>74</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C76" s="13">
         <v>-1</v>
@@ -5249,29 +5262,29 @@
         <v>8</v>
       </c>
       <c r="L76" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"Drawbar 16", </v>
       </c>
       <c r="M76" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N76" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O76" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"Drawbar 16", -1, -1, 16, NULL, tm_drawbar, 0, 127, 0},  // Idx 74</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>75</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C77" s="13">
         <v>-1</v>
@@ -5299,29 +5312,29 @@
         <v>8</v>
       </c>
       <c r="L77" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"Drawbar 5 1/3", </v>
       </c>
       <c r="M77" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N77" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O77" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"Drawbar 5 1/3", -1, -1, 17, NULL, tm_drawbar, 0, 127, 0},  // Idx 75</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>76</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C78" s="13">
         <v>-1</v>
@@ -5349,29 +5362,29 @@
         <v>8</v>
       </c>
       <c r="L78" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"Drawbar 8", </v>
       </c>
       <c r="M78" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N78" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O78" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"Drawbar 8", -1, -1, 18, NULL, tm_drawbar, 0, 127, 0},  // Idx 76</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>77</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C79" s="13">
         <v>-1</v>
@@ -5399,29 +5412,29 @@
         <v>8</v>
       </c>
       <c r="L79" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"Drawbar 4", </v>
       </c>
       <c r="M79" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N79" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O79" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"Drawbar 4", -1, -1, 19, NULL, tm_drawbar, 0, 127, 0},  // Idx 77</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>78</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C80" s="13">
         <v>-1</v>
@@ -5449,29 +5462,29 @@
         <v>8</v>
       </c>
       <c r="L80" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"Drawbar 2 2/3", </v>
       </c>
       <c r="M80" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N80" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O80" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"Drawbar 2 2/3", -1, -1, 20, NULL, tm_drawbar, 0, 127, 0},  // Idx 78</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>79</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C81" s="13">
         <v>-1</v>
@@ -5499,29 +5512,29 @@
         <v>8</v>
       </c>
       <c r="L81" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"Drawbar 2", </v>
       </c>
       <c r="M81" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N81" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O81" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"Drawbar 2", -1, -1, 21, NULL, tm_drawbar, 0, 127, 0},  // Idx 79</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>80</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C82" s="13">
         <v>-1</v>
@@ -5549,29 +5562,29 @@
         <v>8</v>
       </c>
       <c r="L82" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"Drawbar 1 3/5", </v>
       </c>
       <c r="M82" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N82" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O82" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"Drawbar 1 3/5", -1, -1, 22, NULL, tm_drawbar, 0, 127, 0},  // Idx 80</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>81</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C83" s="13">
         <v>-1</v>
@@ -5599,29 +5612,29 @@
         <v>8</v>
       </c>
       <c r="L83" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"Drawbar 1 1/3", </v>
       </c>
       <c r="M83" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N83" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O83" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"Drawbar 1 1/3", -1, -1, 23, NULL, tm_drawbar, 0, 127, 0},  // Idx 81</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>82</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C84" s="13">
         <v>-1</v>
@@ -5649,29 +5662,29 @@
         <v>8</v>
       </c>
       <c r="L84" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"Drawbar 1", </v>
       </c>
       <c r="M84" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N84" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O84" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"Drawbar 1", -1, -1, 24, NULL, tm_drawbar, 0, 127, 0},  // Idx 82</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>83</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C85" s="13">
         <v>-1</v>
@@ -5699,29 +5712,29 @@
         <v>8</v>
       </c>
       <c r="L85" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"Drawbar Mix 1", </v>
       </c>
       <c r="M85" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N85" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O85" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"Drawbar Mix 1", -1, -1, 25, NULL, tm_drawbar, 0, 127, 1},  // Idx 83</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>84</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C86" s="13">
         <v>-1</v>
@@ -5749,29 +5762,29 @@
         <v>8</v>
       </c>
       <c r="L86" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"Drawbar Mix 2", </v>
       </c>
       <c r="M86" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N86" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O86" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"Drawbar Mix 2", -1, -1, 26, NULL, tm_drawbar, 0, 127, 1},  // Idx 84</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>85</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C87" s="13">
         <v>-1</v>
@@ -5799,29 +5812,29 @@
         <v>8</v>
       </c>
       <c r="L87" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"Drawbar Mix 3", </v>
       </c>
       <c r="M87" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N87" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O87" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"Drawbar Mix 3", -1, -1, 27, NULL, tm_drawbar, 0, 127, 1},  // Idx 85</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>86</v>
       </c>
-      <c r="B88" s="37" t="s">
-        <v>79</v>
+      <c r="B88" s="35" t="s">
+        <v>77</v>
       </c>
       <c r="C88" s="13">
         <v>-1</v>
@@ -5849,29 +5862,29 @@
         <v>8</v>
       </c>
       <c r="L88" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"GM Prg 1", </v>
       </c>
       <c r="M88" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N88" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O88" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"GM Prg 1", -1, -1, 232, NULL, tm_numeric, 0, 126, 0},  // Idx 86</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>87</v>
       </c>
-      <c r="B89" s="37" t="s">
-        <v>159</v>
+      <c r="B89" s="35" t="s">
+        <v>154</v>
       </c>
       <c r="C89" s="13">
         <v>-1</v>
@@ -5893,35 +5906,35 @@
         <v>233</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K89" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L89" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"GM Level 1", </v>
       </c>
       <c r="M89" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N89" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O89" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"GM Level 1", -1, -1, 233, NULL, tm_pot, 0, 127, 0},  // Idx 87</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>88</v>
       </c>
-      <c r="B90" s="37" t="s">
-        <v>83</v>
+      <c r="B90" s="35" t="s">
+        <v>81</v>
       </c>
       <c r="C90" s="13">
         <v>-1</v>
@@ -5949,29 +5962,29 @@
         <v>8</v>
       </c>
       <c r="L90" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"GM Harm1", </v>
       </c>
       <c r="M90" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N90" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O90" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"GM Harm1", -1, -1, 234, NULL, tm_numeric, 0, 5, 0},  // Idx 88</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>89</v>
       </c>
-      <c r="B91" s="37" t="s">
-        <v>81</v>
+      <c r="B91" s="35" t="s">
+        <v>79</v>
       </c>
       <c r="C91" s="13">
         <v>-1</v>
@@ -5999,29 +6012,29 @@
         <v>8</v>
       </c>
       <c r="L91" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"GM Prg 2", </v>
       </c>
       <c r="M91" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N91" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O91" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"GM Prg 2", -1, -1, 235, NULL, tm_numeric, 0, 126, 1},  // Idx 89</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>90</v>
       </c>
-      <c r="B92" s="37" t="s">
-        <v>160</v>
+      <c r="B92" s="35" t="s">
+        <v>155</v>
       </c>
       <c r="C92" s="13">
         <v>-1</v>
@@ -6043,35 +6056,35 @@
         <v>236</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K92" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L92" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"GM Level 2", </v>
       </c>
       <c r="M92" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N92" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O92" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"GM Level 2", -1, -1, 236, NULL, tm_pot, 0, 127, 1},  // Idx 90</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>91</v>
       </c>
-      <c r="B93" s="37" t="s">
-        <v>82</v>
+      <c r="B93" s="35" t="s">
+        <v>80</v>
       </c>
       <c r="C93" s="13">
         <v>-1</v>
@@ -6099,29 +6112,29 @@
         <v>8</v>
       </c>
       <c r="L93" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"GM Harm2", </v>
       </c>
       <c r="M93" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N93" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O93" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"GM Harm2", -1, -1, 237, NULL, tm_numeric, 0, 5, 1},  // Idx 91</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>92</v>
       </c>
-      <c r="B94" s="37" t="s">
-        <v>119</v>
+      <c r="B94" s="35" t="s">
+        <v>114</v>
       </c>
       <c r="C94" s="13">
         <v>-1</v>
@@ -6143,35 +6156,35 @@
         <v>238</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K94" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L94" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">"GM Detune 2", </v>
       </c>
       <c r="M94" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N94" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O94" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"GM Detune 2", -1, -1, 238, NULL, tm_pot, 0, 15, 1},  // Idx 92</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>93</v>
       </c>
-      <c r="B95" s="41" t="s">
-        <v>107</v>
+      <c r="B95" s="39" t="s">
+        <v>102</v>
       </c>
       <c r="C95" s="13">
         <v>-1</v>
@@ -6193,35 +6206,35 @@
         <v>56</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K95" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L95" s="11" t="str">
-        <f t="shared" ref="L95:L115" si="25">CONCATENATE("""",B95,""", ")</f>
+        <f t="shared" ref="L95:L115" si="26">CONCATENATE("""",B95,""", ")</f>
         <v xml:space="preserve">"Attack", </v>
       </c>
       <c r="M95" s="11" t="str">
-        <f t="shared" ref="M95:M115" si="26">IF(K95="NULL",CONCATENATE(K95,", "),CONCATENATE("&amp;",K95,", "))</f>
+        <f t="shared" ref="M95:M115" si="27">IF(K95="NULL",CONCATENATE(K95,", "),CONCATENATE("&amp;",K95,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N95" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O95" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v xml:space="preserve">  {"Attack", -1, -1, 56, NULL, tm_pot, 0, 127, 1},  // Idx 93</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>94</v>
       </c>
-      <c r="B96" s="41" t="s">
-        <v>108</v>
+      <c r="B96" s="39" t="s">
+        <v>103</v>
       </c>
       <c r="C96" s="13">
         <v>-1</v>
@@ -6243,35 +6256,35 @@
         <v>57</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K96" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L96" s="11" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">"Decay", </v>
+      </c>
+      <c r="M96" s="11" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N96" s="11" t="str">
+        <f t="shared" si="24"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O96" s="10" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">"Decay", </v>
-      </c>
-      <c r="M96" s="11" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N96" s="11" t="str">
-        <f t="shared" si="23"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O96" s="10" t="str">
-        <f t="shared" si="24"/>
         <v xml:space="preserve">  {"Decay", -1, -1, 57, NULL, tm_pot, 0, 127, 1},  // Idx 94</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>95</v>
       </c>
-      <c r="B97" s="41" t="s">
-        <v>109</v>
+      <c r="B97" s="39" t="s">
+        <v>104</v>
       </c>
       <c r="C97" s="13">
         <v>-1</v>
@@ -6293,35 +6306,35 @@
         <v>58</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K97" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L97" s="11" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">"Sustain", </v>
+      </c>
+      <c r="M97" s="11" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N97" s="11" t="str">
+        <f t="shared" si="24"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O97" s="10" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">"Sustain", </v>
-      </c>
-      <c r="M97" s="11" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N97" s="11" t="str">
-        <f t="shared" si="23"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O97" s="10" t="str">
-        <f t="shared" si="24"/>
         <v xml:space="preserve">  {"Sustain", -1, -1, 58, NULL, tm_pot, 0, 127, 1},  // Idx 95</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>96</v>
       </c>
-      <c r="B98" s="41" t="s">
-        <v>110</v>
+      <c r="B98" s="39" t="s">
+        <v>105</v>
       </c>
       <c r="C98" s="13">
         <v>-1</v>
@@ -6343,35 +6356,35 @@
         <v>59</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K98" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L98" s="11" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">"Release", </v>
+      </c>
+      <c r="M98" s="11" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N98" s="11" t="str">
+        <f t="shared" si="24"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O98" s="10" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">"Release", </v>
-      </c>
-      <c r="M98" s="11" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N98" s="11" t="str">
-        <f t="shared" si="23"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O98" s="10" t="str">
-        <f t="shared" si="24"/>
         <v xml:space="preserve">  {"Release", -1, -1, 59, NULL, tm_pot, 0, 127, 1},  // Idx 96</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>97</v>
       </c>
-      <c r="B99" s="41" t="s">
-        <v>111</v>
+      <c r="B99" s="39" t="s">
+        <v>106</v>
       </c>
       <c r="C99" s="13">
         <v>-1</v>
@@ -6393,35 +6406,35 @@
         <v>60</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K99" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L99" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"ADSR Harmonic", </v>
       </c>
       <c r="M99" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N99" s="11" t="str">
-        <f t="shared" ref="N99:N130" si="27">IF(J99="NULL",CONCATENATE(J99,", "),CONCATENATE("tm_",J99,", "))</f>
+        <f t="shared" ref="N99:N130" si="28">IF(J99="NULL",CONCATENATE(J99,", "),CONCATENATE("tm_",J99,", "))</f>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O99" s="10" t="str">
-        <f t="shared" ref="O99:O130" si="28">CONCATENATE("  {",L99,C99,", ",D99,", ",I99,", ",M99,N99,F99,", ",G99,", ",H99,"},  // Idx ", A99)</f>
+        <f t="shared" ref="O99:O130" si="29">CONCATENATE("  {",L99,C99,", ",D99,", ",I99,", ",M99,N99,F99,", ",G99,", ",H99,"},  // Idx ", A99)</f>
         <v xml:space="preserve">  {"ADSR Harmonic", -1, -1, 60, NULL, tm_pot, 0, 127, 1},  // Idx 97</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>98</v>
       </c>
-      <c r="B100" s="41" t="s">
-        <v>98</v>
+      <c r="B100" s="39" t="s">
+        <v>93</v>
       </c>
       <c r="C100" s="13">
         <v>-1</v>
@@ -6449,29 +6462,29 @@
         <v>8</v>
       </c>
       <c r="L100" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"ADSR on 16", </v>
       </c>
       <c r="M100" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N100" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O100" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"ADSR on 16", -1, -1, 176, NULL, tm_tab, 0, 1, 1},  // Idx 98</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>99</v>
       </c>
-      <c r="B101" s="41" t="s">
-        <v>99</v>
+      <c r="B101" s="39" t="s">
+        <v>94</v>
       </c>
       <c r="C101" s="13">
         <v>-1</v>
@@ -6499,29 +6512,29 @@
         <v>8</v>
       </c>
       <c r="L101" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"ADSR on 5 1/3", </v>
       </c>
       <c r="M101" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N101" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O101" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"ADSR on 5 1/3", -1, -1, 177, NULL, tm_tab, 0, 1, 1},  // Idx 99</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>100</v>
       </c>
-      <c r="B102" s="41" t="s">
-        <v>100</v>
+      <c r="B102" s="39" t="s">
+        <v>95</v>
       </c>
       <c r="C102" s="13">
         <v>-1</v>
@@ -6549,29 +6562,29 @@
         <v>8</v>
       </c>
       <c r="L102" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"ADSR on 8", </v>
       </c>
       <c r="M102" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N102" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O102" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"ADSR on 8", -1, -1, 178, NULL, tm_tab, 0, 1, 1},  // Idx 100</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>101</v>
       </c>
-      <c r="B103" s="41" t="s">
-        <v>101</v>
+      <c r="B103" s="39" t="s">
+        <v>96</v>
       </c>
       <c r="C103" s="13">
         <v>-1</v>
@@ -6599,29 +6612,29 @@
         <v>8</v>
       </c>
       <c r="L103" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"ADSR on 4", </v>
       </c>
       <c r="M103" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N103" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O103" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"ADSR on 4", -1, -1, 179, NULL, tm_tab, 0, 1, 1},  // Idx 101</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>102</v>
       </c>
-      <c r="B104" s="41" t="s">
-        <v>102</v>
+      <c r="B104" s="39" t="s">
+        <v>97</v>
       </c>
       <c r="C104" s="13">
         <v>-1</v>
@@ -6649,29 +6662,29 @@
         <v>8</v>
       </c>
       <c r="L104" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"ADSR on 2 2/3", </v>
       </c>
       <c r="M104" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N104" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O104" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"ADSR on 2 2/3", -1, -1, 180, NULL, tm_tab, 0, 1, 1},  // Idx 102</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>103</v>
       </c>
-      <c r="B105" s="41" t="s">
-        <v>103</v>
+      <c r="B105" s="39" t="s">
+        <v>98</v>
       </c>
       <c r="C105" s="13">
         <v>-1</v>
@@ -6699,29 +6712,29 @@
         <v>8</v>
       </c>
       <c r="L105" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"ADSR on 2", </v>
       </c>
       <c r="M105" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N105" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O105" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"ADSR on 2", -1, -1, 181, NULL, tm_tab, 0, 1, 1},  // Idx 103</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>104</v>
       </c>
-      <c r="B106" s="41" t="s">
-        <v>104</v>
+      <c r="B106" s="39" t="s">
+        <v>99</v>
       </c>
       <c r="C106" s="13">
         <v>-1</v>
@@ -6749,29 +6762,29 @@
         <v>8</v>
       </c>
       <c r="L106" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"ADSR on 1 3/5", </v>
       </c>
       <c r="M106" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N106" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O106" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"ADSR on 1 3/5", -1, -1, 182, NULL, tm_tab, 0, 1, 1},  // Idx 104</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>105</v>
       </c>
-      <c r="B107" s="41" t="s">
-        <v>105</v>
+      <c r="B107" s="39" t="s">
+        <v>100</v>
       </c>
       <c r="C107" s="13">
         <v>-1</v>
@@ -6799,29 +6812,29 @@
         <v>8</v>
       </c>
       <c r="L107" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"ADSR on 1 1/3", </v>
       </c>
       <c r="M107" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N107" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O107" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"ADSR on 1 1/3", -1, -1, 183, NULL, tm_tab, 0, 1, 1},  // Idx 105</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>106</v>
       </c>
-      <c r="B108" s="41" t="s">
-        <v>106</v>
+      <c r="B108" s="39" t="s">
+        <v>101</v>
       </c>
       <c r="C108" s="13">
         <v>-1</v>
@@ -6849,29 +6862,29 @@
         <v>8</v>
       </c>
       <c r="L108" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"ADSR on 1", </v>
       </c>
       <c r="M108" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N108" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O108" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"ADSR on 1", -1, -1, 184, NULL, tm_tab, 0, 1, 1},  // Idx 106</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>107</v>
       </c>
-      <c r="B109" s="41" t="s">
-        <v>115</v>
+      <c r="B109" s="39" t="s">
+        <v>110</v>
       </c>
       <c r="C109" s="13">
         <v>-1</v>
@@ -6899,29 +6912,29 @@
         <v>8</v>
       </c>
       <c r="L109" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"ADSR on Mix 1", </v>
       </c>
       <c r="M109" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N109" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O109" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"ADSR on Mix 1", -1, -1, 185, NULL, tm_tab, 0, 1, 1},  // Idx 107</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>108</v>
       </c>
-      <c r="B110" s="41" t="s">
-        <v>116</v>
+      <c r="B110" s="39" t="s">
+        <v>111</v>
       </c>
       <c r="C110" s="13">
         <v>-1</v>
@@ -6949,29 +6962,29 @@
         <v>8</v>
       </c>
       <c r="L110" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"ADSR on Mix 2", </v>
       </c>
       <c r="M110" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N110" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O110" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"ADSR on Mix 2", -1, -1, 186, NULL, tm_tab, 0, 1, 1},  // Idx 108</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>109</v>
       </c>
-      <c r="B111" s="41" t="s">
-        <v>117</v>
+      <c r="B111" s="39" t="s">
+        <v>112</v>
       </c>
       <c r="C111" s="13">
         <v>-1</v>
@@ -6999,29 +7012,29 @@
         <v>8</v>
       </c>
       <c r="L111" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"ADSR on Mix 3", </v>
       </c>
       <c r="M111" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N111" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O111" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"ADSR on Mix 3", -1, -1, 187, NULL, tm_tab, 0, 1, 1},  // Idx 109</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>110</v>
       </c>
-      <c r="B112" s="28" t="s">
-        <v>67</v>
+      <c r="B112" s="27" t="s">
+        <v>65</v>
       </c>
       <c r="C112" s="13">
         <v>-1</v>
@@ -7049,29 +7062,29 @@
         <v>8</v>
       </c>
       <c r="L112" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"Drawbar 16", </v>
       </c>
       <c r="M112" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N112" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O112" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"Drawbar 16", -1, -1, 72, NULL, tm_drawbar, 0, 127, 0},  // Idx 110</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>111</v>
       </c>
-      <c r="B113" s="28" t="s">
-        <v>189</v>
+      <c r="B113" s="27" t="s">
+        <v>183</v>
       </c>
       <c r="C113" s="13">
         <v>-1</v>
@@ -7099,29 +7112,29 @@
         <v>8</v>
       </c>
       <c r="L113" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"Drawbar 16H", </v>
       </c>
       <c r="M113" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N113" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O113" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"Drawbar 16H", -1, -1, 73, NULL, tm_drawbar, 0, 127, 0},  // Idx 111</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>112</v>
       </c>
-      <c r="B114" s="28" t="s">
-        <v>69</v>
+      <c r="B114" s="27" t="s">
+        <v>67</v>
       </c>
       <c r="C114" s="13">
         <v>-1</v>
@@ -7149,29 +7162,29 @@
         <v>8</v>
       </c>
       <c r="L114" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"Drawbar 8", </v>
       </c>
       <c r="M114" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N114" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O114" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"Drawbar 8", -1, -1, 74, NULL, tm_drawbar, 0, 127, 0},  // Idx 112</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>113</v>
       </c>
-      <c r="B115" s="28" t="s">
-        <v>190</v>
+      <c r="B115" s="27" t="s">
+        <v>184</v>
       </c>
       <c r="C115" s="13">
         <v>-1</v>
@@ -7199,29 +7212,29 @@
         <v>8</v>
       </c>
       <c r="L115" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"Drawbar 8H", </v>
       </c>
       <c r="M115" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N115" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O115" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"Drawbar 8H", -1, -1, 75, NULL, tm_drawbar, 0, 127, 0},  // Idx 113</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>114</v>
       </c>
-      <c r="B116" s="28" t="s">
-        <v>110</v>
+      <c r="B116" s="27" t="s">
+        <v>105</v>
       </c>
       <c r="C116" s="13">
         <v>-1</v>
@@ -7257,21 +7270,21 @@
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N116" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_drawbar, </v>
       </c>
       <c r="O116" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"Release", -1, -1, 67, NULL, tm_drawbar, 0, 127, 0},  // Idx 114</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>115</v>
       </c>
-      <c r="B117" s="38" t="s">
-        <v>79</v>
+      <c r="B117" s="36" t="s">
+        <v>77</v>
       </c>
       <c r="C117" s="13">
         <v>-1</v>
@@ -7299,29 +7312,29 @@
         <v>8</v>
       </c>
       <c r="L117" s="11" t="str">
-        <f t="shared" ref="L117:L123" si="29">CONCATENATE("""",B117,""", ")</f>
+        <f t="shared" ref="L117:L123" si="30">CONCATENATE("""",B117,""", ")</f>
         <v xml:space="preserve">"GM Prg 1", </v>
       </c>
       <c r="M117" s="11" t="str">
-        <f t="shared" ref="M117:M123" si="30">IF(K117="NULL",CONCATENATE(K117,", "),CONCATENATE("&amp;",K117,", "))</f>
+        <f t="shared" ref="M117:M123" si="31">IF(K117="NULL",CONCATENATE(K117,", "),CONCATENATE("&amp;",K117,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N117" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O117" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"GM Prg 1", -1, -1, 240, NULL, tm_numeric, 0, 126, 0},  // Idx 115</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>116</v>
       </c>
-      <c r="B118" s="38" t="s">
-        <v>159</v>
+      <c r="B118" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="C118" s="13">
         <v>-1</v>
@@ -7343,35 +7356,35 @@
         <v>241</v>
       </c>
       <c r="J118" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K118" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L118" s="11" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">"GM Level 1", </v>
+      </c>
+      <c r="M118" s="11" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N118" s="11" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O118" s="10" t="str">
         <f t="shared" si="29"/>
-        <v xml:space="preserve">"GM Level 1", </v>
-      </c>
-      <c r="M118" s="11" t="str">
-        <f t="shared" si="30"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N118" s="11" t="str">
-        <f t="shared" si="27"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O118" s="10" t="str">
-        <f t="shared" si="28"/>
         <v xml:space="preserve">  {"GM Level 1", -1, -1, 241, NULL, tm_pot, 0, 127, 0},  // Idx 116</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>117</v>
       </c>
-      <c r="B119" s="38" t="s">
-        <v>83</v>
+      <c r="B119" s="36" t="s">
+        <v>81</v>
       </c>
       <c r="C119" s="13">
         <v>-1</v>
@@ -7399,29 +7412,29 @@
         <v>8</v>
       </c>
       <c r="L119" s="11" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">"GM Harm1", </v>
+      </c>
+      <c r="M119" s="11" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N119" s="11" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">tm_numeric, </v>
+      </c>
+      <c r="O119" s="10" t="str">
         <f t="shared" si="29"/>
-        <v xml:space="preserve">"GM Harm1", </v>
-      </c>
-      <c r="M119" s="11" t="str">
-        <f t="shared" si="30"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N119" s="11" t="str">
-        <f t="shared" si="27"/>
-        <v xml:space="preserve">tm_numeric, </v>
-      </c>
-      <c r="O119" s="10" t="str">
-        <f t="shared" si="28"/>
         <v xml:space="preserve">  {"GM Harm1", -1, -1, 242, NULL, tm_numeric, 0, 5, 0},  // Idx 117</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>118</v>
       </c>
-      <c r="B120" s="38" t="s">
-        <v>81</v>
+      <c r="B120" s="36" t="s">
+        <v>79</v>
       </c>
       <c r="C120" s="13">
         <v>-1</v>
@@ -7449,29 +7462,29 @@
         <v>8</v>
       </c>
       <c r="L120" s="11" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">"GM Prg 2", </v>
+      </c>
+      <c r="M120" s="11" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N120" s="11" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">tm_numeric, </v>
+      </c>
+      <c r="O120" s="10" t="str">
         <f t="shared" si="29"/>
-        <v xml:space="preserve">"GM Prg 2", </v>
-      </c>
-      <c r="M120" s="11" t="str">
-        <f t="shared" si="30"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N120" s="11" t="str">
-        <f t="shared" si="27"/>
-        <v xml:space="preserve">tm_numeric, </v>
-      </c>
-      <c r="O120" s="10" t="str">
-        <f t="shared" si="28"/>
         <v xml:space="preserve">  {"GM Prg 2", -1, -1, 243, NULL, tm_numeric, 0, 126, 1},  // Idx 118</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>119</v>
       </c>
-      <c r="B121" s="38" t="s">
-        <v>160</v>
+      <c r="B121" s="36" t="s">
+        <v>155</v>
       </c>
       <c r="C121" s="13">
         <v>-1</v>
@@ -7493,35 +7506,35 @@
         <v>244</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K121" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L121" s="11" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">"GM Level 2", </v>
+      </c>
+      <c r="M121" s="11" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N121" s="11" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O121" s="10" t="str">
         <f t="shared" si="29"/>
-        <v xml:space="preserve">"GM Level 2", </v>
-      </c>
-      <c r="M121" s="11" t="str">
-        <f t="shared" si="30"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N121" s="11" t="str">
-        <f t="shared" si="27"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O121" s="10" t="str">
-        <f t="shared" si="28"/>
         <v xml:space="preserve">  {"GM Level 2", -1, -1, 244, NULL, tm_pot, 0, 127, 1},  // Idx 119</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>120</v>
       </c>
-      <c r="B122" s="38" t="s">
-        <v>82</v>
+      <c r="B122" s="36" t="s">
+        <v>80</v>
       </c>
       <c r="C122" s="13">
         <v>-1</v>
@@ -7549,29 +7562,29 @@
         <v>8</v>
       </c>
       <c r="L122" s="11" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">"GM Harm2", </v>
+      </c>
+      <c r="M122" s="11" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N122" s="11" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">tm_numeric, </v>
+      </c>
+      <c r="O122" s="10" t="str">
         <f t="shared" si="29"/>
-        <v xml:space="preserve">"GM Harm2", </v>
-      </c>
-      <c r="M122" s="11" t="str">
-        <f t="shared" si="30"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N122" s="11" t="str">
-        <f t="shared" si="27"/>
-        <v xml:space="preserve">tm_numeric, </v>
-      </c>
-      <c r="O122" s="10" t="str">
-        <f t="shared" si="28"/>
         <v xml:space="preserve">  {"GM Harm2", -1, -1, 245, NULL, tm_numeric, 0, 5, 1},  // Idx 120</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>121</v>
       </c>
-      <c r="B123" s="38" t="s">
-        <v>119</v>
+      <c r="B123" s="36" t="s">
+        <v>114</v>
       </c>
       <c r="C123" s="13">
         <v>-1</v>
@@ -7593,35 +7606,35 @@
         <v>246</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K123" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L123" s="11" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">"GM Detune 2", </v>
+      </c>
+      <c r="M123" s="11" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N123" s="11" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O123" s="10" t="str">
         <f t="shared" si="29"/>
-        <v xml:space="preserve">"GM Detune 2", </v>
-      </c>
-      <c r="M123" s="11" t="str">
-        <f t="shared" si="30"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N123" s="11" t="str">
-        <f t="shared" si="27"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O123" s="10" t="str">
-        <f t="shared" si="28"/>
         <v xml:space="preserve">  {"GM Detune 2", -1, -1, 246, NULL, tm_pot, 0, 15, 1},  // Idx 121</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>122</v>
       </c>
-      <c r="B124" s="42" t="s">
-        <v>107</v>
+      <c r="B124" s="40" t="s">
+        <v>102</v>
       </c>
       <c r="C124" s="13">
         <v>-1</v>
@@ -7643,35 +7656,35 @@
         <v>64</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K124" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L124" s="11" t="str">
-        <f t="shared" ref="L124:L128" si="31">CONCATENATE("""",B124,""", ")</f>
+        <f t="shared" ref="L124:L128" si="32">CONCATENATE("""",B124,""", ")</f>
         <v xml:space="preserve">"Attack", </v>
       </c>
       <c r="M124" s="11" t="str">
-        <f t="shared" ref="M124:M128" si="32">IF(K124="NULL",CONCATENATE(K124,", "),CONCATENATE("&amp;",K124,", "))</f>
+        <f t="shared" ref="M124:M128" si="33">IF(K124="NULL",CONCATENATE(K124,", "),CONCATENATE("&amp;",K124,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N124" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O124" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"Attack", -1, -1, 64, NULL, tm_pot, 0, 127, 1},  // Idx 122</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>123</v>
       </c>
-      <c r="B125" s="42" t="s">
-        <v>108</v>
+      <c r="B125" s="40" t="s">
+        <v>103</v>
       </c>
       <c r="C125" s="13">
         <v>-1</v>
@@ -7693,35 +7706,35 @@
         <v>65</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K125" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L125" s="11" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v xml:space="preserve">"Decay", </v>
       </c>
       <c r="M125" s="11" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N125" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O125" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"Decay", -1, -1, 65, NULL, tm_pot, 0, 127, 1},  // Idx 123</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="16">
-        <f t="shared" ref="A126:A201" si="33">A125+1</f>
+        <f t="shared" ref="A126:A201" si="34">A125+1</f>
         <v>124</v>
       </c>
-      <c r="B126" s="42" t="s">
-        <v>109</v>
+      <c r="B126" s="40" t="s">
+        <v>104</v>
       </c>
       <c r="C126" s="13">
         <v>-1</v>
@@ -7743,35 +7756,35 @@
         <v>66</v>
       </c>
       <c r="J126" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K126" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L126" s="11" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v xml:space="preserve">"Sustain", </v>
       </c>
       <c r="M126" s="11" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N126" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O126" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"Sustain", -1, -1, 66, NULL, tm_pot, 0, 127, 1},  // Idx 124</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>125</v>
       </c>
-      <c r="B127" s="42" t="s">
-        <v>110</v>
+      <c r="B127" s="40" t="s">
+        <v>105</v>
       </c>
       <c r="C127" s="13">
         <v>-1</v>
@@ -7793,35 +7806,35 @@
         <v>67</v>
       </c>
       <c r="J127" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K127" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L127" s="11" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v xml:space="preserve">"Release", </v>
       </c>
       <c r="M127" s="11" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N127" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O127" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"Release", -1, -1, 67, NULL, tm_pot, 0, 127, 1},  // Idx 125</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>126</v>
       </c>
-      <c r="B128" s="42" t="s">
-        <v>111</v>
+      <c r="B128" s="40" t="s">
+        <v>106</v>
       </c>
       <c r="C128" s="13">
         <v>-1</v>
@@ -7843,35 +7856,35 @@
         <v>68</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K128" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L128" s="11" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v xml:space="preserve">"ADSR Harmonic", </v>
       </c>
       <c r="M128" s="11" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N128" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O128" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"ADSR Harmonic", -1, -1, 68, NULL, tm_pot, 0, 127, 1},  // Idx 126</v>
       </c>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>127</v>
       </c>
-      <c r="B129" s="29" t="s">
-        <v>155</v>
+      <c r="B129" s="28" t="s">
+        <v>150</v>
       </c>
       <c r="C129" s="13">
         <v>-1</v>
@@ -7899,28 +7912,28 @@
         <v>8</v>
       </c>
       <c r="L129" s="11" t="str">
-        <f t="shared" ref="L129:L135" si="34">CONCATENATE("""",B129,""", ")</f>
+        <f t="shared" ref="L129:L135" si="35">CONCATENATE("""",B129,""", ")</f>
         <v xml:space="preserve">"Percussion", </v>
       </c>
       <c r="M129" s="11" t="str">
-        <f t="shared" ref="M129:M135" si="35">IF(K129="NULL",CONCATENATE(K129,", "),CONCATENATE("&amp;",K129,", "))</f>
+        <f t="shared" ref="M129:M135" si="36">IF(K129="NULL",CONCATENATE(K129,", "),CONCATENATE("&amp;",K129,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N129" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O129" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"Percussion", -1, -1, 128, NULL, tm_tab, 0, 1, 0},  // Idx 127</v>
       </c>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>128</v>
       </c>
-      <c r="B130" s="29" t="s">
+      <c r="B130" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C130" s="13">
@@ -7949,28 +7962,28 @@
         <v>8</v>
       </c>
       <c r="L130" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v xml:space="preserve">"Perc Soft", </v>
       </c>
       <c r="M130" s="11" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N130" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O130" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v xml:space="preserve">  {"Perc Soft", -1, -1, 129, NULL, tm_tab, 0, 1, 0},  // Idx 128</v>
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>129</v>
       </c>
-      <c r="B131" s="29" t="s">
+      <c r="B131" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C131" s="13">
@@ -7999,28 +8012,28 @@
         <v>8</v>
       </c>
       <c r="L131" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v xml:space="preserve">"Perc Fast", </v>
       </c>
       <c r="M131" s="11" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N131" s="11" t="str">
-        <f t="shared" ref="N131:N137" si="36">IF(J131="NULL",CONCATENATE(J131,", "),CONCATENATE("tm_",J131,", "))</f>
+        <f t="shared" ref="N131:N137" si="37">IF(J131="NULL",CONCATENATE(J131,", "),CONCATENATE("tm_",J131,", "))</f>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O131" s="10" t="str">
-        <f t="shared" ref="O131:O162" si="37">CONCATENATE("  {",L131,C131,", ",D131,", ",I131,", ",M131,N131,F131,", ",G131,", ",H131,"},  // Idx ", A131)</f>
+        <f t="shared" ref="O131:O137" si="38">CONCATENATE("  {",L131,C131,", ",D131,", ",I131,", ",M131,N131,F131,", ",G131,", ",H131,"},  // Idx ", A131)</f>
         <v xml:space="preserve">  {"Perc Fast", -1, -1, 130, NULL, tm_tab, 0, 1, 0},  // Idx 129</v>
       </c>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>130</v>
       </c>
-      <c r="B132" s="29" t="s">
+      <c r="B132" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C132" s="13">
@@ -8049,29 +8062,29 @@
         <v>8</v>
       </c>
       <c r="L132" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v xml:space="preserve">"Perc Third", </v>
       </c>
       <c r="M132" s="11" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N132" s="11" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O132" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">  {"Perc Third", -1, -1, 131, NULL, tm_tab, 0, 1, 0},  // Idx 130</v>
       </c>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>131</v>
       </c>
-      <c r="B133" s="29" t="s">
-        <v>20</v>
+      <c r="B133" s="28" t="s">
+        <v>21</v>
       </c>
       <c r="C133" s="13">
         <v>-1</v>
@@ -8090,7 +8103,7 @@
         <v>0</v>
       </c>
       <c r="I133" s="5">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J133" s="7" t="s">
         <v>28</v>
@@ -8099,29 +8112,29 @@
         <v>8</v>
       </c>
       <c r="L133" s="11" t="str">
-        <f t="shared" si="34"/>
-        <v xml:space="preserve">"Vib On Lower", </v>
+        <f>CONCATENATE("""",B133,""", ")</f>
+        <v xml:space="preserve">"Vib On Upper", </v>
       </c>
       <c r="M133" s="11" t="str">
-        <f t="shared" si="35"/>
+        <f>IF(K133="NULL",CONCATENATE(K133,", "),CONCATENATE("&amp;",K133,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N133" s="11" t="str">
-        <f t="shared" si="36"/>
+        <f>IF(J133="NULL",CONCATENATE(J133,", "),CONCATENATE("tm_",J133,", "))</f>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O133" s="10" t="str">
-        <f t="shared" si="37"/>
-        <v xml:space="preserve">  {"Vib On Lower", -1, -1, 133, NULL, tm_tab, 0, 1, 0},  // Idx 131</v>
+        <f>CONCATENATE("  {",L133,C133,", ",D133,", ",I133,", ",M133,N133,F133,", ",G133,", ",H133,"},  // Idx ", A133)</f>
+        <v xml:space="preserve">  {"Vib On Upper", -1, -1, 132, NULL, tm_tab, 0, 1, 0},  // Idx 131</v>
       </c>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>132</v>
       </c>
-      <c r="B134" s="29" t="s">
-        <v>21</v>
+      <c r="B134" s="28" t="s">
+        <v>20</v>
       </c>
       <c r="C134" s="13">
         <v>-1</v>
@@ -8140,7 +8153,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="5">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J134" s="7" t="s">
         <v>28</v>
@@ -8149,28 +8162,28 @@
         <v>8</v>
       </c>
       <c r="L134" s="11" t="str">
-        <f t="shared" si="34"/>
-        <v xml:space="preserve">"Vib On Upper", </v>
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">"Vib On Lower", </v>
       </c>
       <c r="M134" s="11" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N134" s="11" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O134" s="10" t="str">
-        <f t="shared" si="37"/>
-        <v xml:space="preserve">  {"Vib On Upper", -1, -1, 134, NULL, tm_tab, 0, 1, 0},  // Idx 132</v>
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">  {"Vib On Lower", -1, -1, 133, NULL, tm_tab, 0, 1, 0},  // Idx 132</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>133</v>
       </c>
-      <c r="B135" s="29" t="s">
+      <c r="B135" s="28" t="s">
         <v>19</v>
       </c>
       <c r="C135" s="13">
@@ -8193,35 +8206,35 @@
         <v>264</v>
       </c>
       <c r="J135" s="7" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="K135" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L135" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v xml:space="preserve">"Vib Knob", </v>
       </c>
       <c r="M135" s="11" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N135" s="11" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v xml:space="preserve">tm_vibknob, </v>
       </c>
       <c r="O135" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">  {"Vib Knob", -1, -1, 264, NULL, tm_vibknob, 0, 5, 0},  // Idx 133</v>
       </c>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>134</v>
       </c>
-      <c r="B136" s="29" t="s">
-        <v>64</v>
+      <c r="B136" s="28" t="s">
+        <v>62</v>
       </c>
       <c r="C136" s="13">
         <v>-1</v>
@@ -8249,29 +8262,29 @@
         <v>8</v>
       </c>
       <c r="L136" s="11" t="str">
-        <f t="shared" ref="L136:L137" si="38">CONCATENATE("""",B136,""", ")</f>
+        <f t="shared" ref="L136:L137" si="39">CONCATENATE("""",B136,""", ")</f>
         <v xml:space="preserve">"H100 2ndVoice", </v>
       </c>
       <c r="M136" s="11" t="str">
-        <f t="shared" ref="M136:M137" si="39">IF(K136="NULL",CONCATENATE(K136,", "),CONCATENATE("&amp;",K136,", "))</f>
+        <f t="shared" ref="M136:M137" si="40">IF(K136="NULL",CONCATENATE(K136,", "),CONCATENATE("&amp;",K136,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N136" s="11" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O136" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">  {"H100 2ndVoice", -1, -1, 156, NULL, tm_tab, 0, 1, 0},  // Idx 134</v>
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>135</v>
       </c>
-      <c r="B137" s="29" t="s">
-        <v>65</v>
+      <c r="B137" s="28" t="s">
+        <v>63</v>
       </c>
       <c r="C137" s="13">
         <v>-1</v>
@@ -8299,29 +8312,29 @@
         <v>8</v>
       </c>
       <c r="L137" s="11" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">"EG DB To Dry ", </v>
+      </c>
+      <c r="M137" s="11" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N137" s="11" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">tm_tab, </v>
+      </c>
+      <c r="O137" s="10" t="str">
         <f t="shared" si="38"/>
-        <v xml:space="preserve">"EG DB To Dry ", </v>
-      </c>
-      <c r="M137" s="11" t="str">
-        <f t="shared" si="39"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N137" s="11" t="str">
-        <f t="shared" si="36"/>
-        <v xml:space="preserve">tm_tab, </v>
-      </c>
-      <c r="O137" s="10" t="str">
-        <f t="shared" si="37"/>
         <v xml:space="preserve">  {"EG DB To Dry ", -1, -1, 158, NULL, tm_tab, 0, 1, 0},  // Idx 135</v>
       </c>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>136</v>
       </c>
-      <c r="B138" s="29" t="s">
-        <v>185</v>
+      <c r="B138" s="28" t="s">
+        <v>179</v>
       </c>
       <c r="C138" s="13">
         <v>-1</v>
@@ -8349,29 +8362,29 @@
         <v>8</v>
       </c>
       <c r="L138" s="11" t="str">
-        <f t="shared" ref="L138:L140" si="40">CONCATENATE("""",B138,""", ")</f>
+        <f t="shared" ref="L138:L140" si="41">CONCATENATE("""",B138,""", ")</f>
         <v xml:space="preserve">"PHR On Upper", </v>
       </c>
       <c r="M138" s="11" t="str">
-        <f t="shared" ref="M138:M140" si="41">IF(K138="NULL",CONCATENATE(K138,", "),CONCATENATE("&amp;",K138,", "))</f>
+        <f t="shared" ref="M138:M140" si="42">IF(K138="NULL",CONCATENATE(K138,", "),CONCATENATE("&amp;",K138,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N138" s="11" t="str">
-        <f t="shared" ref="N138:N140" si="42">IF(J138="NULL",CONCATENATE(J138,", "),CONCATENATE("tm_",J138,", "))</f>
+        <f t="shared" ref="N138:N140" si="43">IF(J138="NULL",CONCATENATE(J138,", "),CONCATENATE("tm_",J138,", "))</f>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O138" s="10" t="str">
-        <f t="shared" ref="O138:O140" si="43">CONCATENATE("  {",L138,C138,", ",D138,", ",I138,", ",M138,N138,F138,", ",G138,", ",H138,"},  // Idx ", A138)</f>
+        <f t="shared" ref="O138:O140" si="44">CONCATENATE("  {",L138,C138,", ",D138,", ",I138,", ",M138,N138,F138,", ",G138,", ",H138,"},  // Idx ", A138)</f>
         <v xml:space="preserve">  {"PHR On Upper", -1, -1, 138, NULL, tm_tab, 0, 1, 1},  // Idx 136</v>
       </c>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>137</v>
       </c>
-      <c r="B139" s="29" t="s">
-        <v>186</v>
+      <c r="B139" s="28" t="s">
+        <v>180</v>
       </c>
       <c r="C139" s="13">
         <v>-1</v>
@@ -8399,29 +8412,29 @@
         <v>8</v>
       </c>
       <c r="L139" s="11" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v xml:space="preserve">"PHR On Lower", </v>
       </c>
       <c r="M139" s="11" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N139" s="11" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O139" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v xml:space="preserve">  {"PHR On Lower", -1, -1, 139, NULL, tm_tab, 0, 1, 1},  // Idx 137</v>
       </c>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>138</v>
       </c>
-      <c r="B140" s="29" t="s">
-        <v>187</v>
+      <c r="B140" s="28" t="s">
+        <v>181</v>
       </c>
       <c r="C140" s="13">
         <v>-1</v>
@@ -8440,38 +8453,38 @@
         <v>1</v>
       </c>
       <c r="I140" s="5">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J140" s="7" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="K140" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L140" s="11" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v xml:space="preserve">"PHR Knob", </v>
       </c>
       <c r="M140" s="11" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N140" s="11" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v xml:space="preserve">tm_phrknob, </v>
       </c>
       <c r="O140" s="10" t="str">
-        <f t="shared" si="43"/>
-        <v xml:space="preserve">  {"PHR Knob", -1, -1, 257, NULL, tm_phrknob, 0, 7, 1},  // Idx 138</v>
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">  {"PHR Knob", -1, -1, 256, NULL, tm_phrknob, 0, 7, 1},  // Idx 138</v>
       </c>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>139</v>
       </c>
-      <c r="B141" s="32" t="s">
-        <v>129</v>
+      <c r="B141" s="31" t="s">
+        <v>124</v>
       </c>
       <c r="C141" s="13">
         <v>-1</v>
@@ -8490,39 +8503,39 @@
         <v>1</v>
       </c>
       <c r="I141" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J141" s="7" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="K141" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L141" s="11" t="str">
-        <f t="shared" ref="L141:L176" si="44">CONCATENATE("""",B141,""", ")</f>
+        <f t="shared" ref="L141:L176" si="45">CONCATENATE("""",B141,""", ")</f>
         <v xml:space="preserve">"Gating Mode", </v>
       </c>
       <c r="M141" s="11" t="str">
-        <f t="shared" ref="M141:M176" si="45">IF(K141="NULL",CONCATENATE(K141,", "),CONCATENATE("&amp;",K141,", "))</f>
+        <f t="shared" ref="M141:M176" si="46">IF(K141="NULL",CONCATENATE(K141,", "),CONCATENATE("&amp;",K141,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N141" s="11" t="str">
-        <f t="shared" ref="N141:N172" si="46">IF(J141="NULL",CONCATENATE(J141,", "),CONCATENATE("tm_",J141,", "))</f>
+        <f t="shared" ref="N141:N172" si="47">IF(J141="NULL",CONCATENATE(J141,", "),CONCATENATE("tm_",J141,", "))</f>
         <v xml:space="preserve">tm_gating, </v>
       </c>
       <c r="O141" s="10" t="str">
-        <f t="shared" ref="O141:O172" si="47">CONCATENATE("  {",L141,C141,", ",D141,", ",I141,", ",M141,N141,F141,", ",G141,", ",H141,"},  // Idx ", A141)</f>
-        <v xml:space="preserve">  {"Gating Mode", -1, -1, 261, NULL, tm_gating, 0, 4, 1},  // Idx 139</v>
+        <f t="shared" ref="O141:O172" si="48">CONCATENATE("  {",L141,C141,", ",D141,", ",I141,", ",M141,N141,F141,", ",G141,", ",H141,"},  // Idx ", A141)</f>
+        <v xml:space="preserve">  {"Gating Mode", -1, -1, 260, NULL, tm_gating, 0, 4, 1},  // Idx 139</v>
       </c>
       <c r="P141" s="6"/>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>140</v>
       </c>
-      <c r="B142" s="32" t="s">
-        <v>130</v>
+      <c r="B142" s="31" t="s">
+        <v>125</v>
       </c>
       <c r="C142" s="13">
         <v>-1</v>
@@ -8544,36 +8557,36 @@
         <v>388</v>
       </c>
       <c r="J142" s="7" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="K142" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L142" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"TG WaveSet", </v>
       </c>
       <c r="M142" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N142" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_waveset, </v>
       </c>
       <c r="O142" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"TG WaveSet", -1, -1, 388, NULL, tm_waveset, 0, 7, 0},  // Idx 140</v>
       </c>
       <c r="P142" s="6"/>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>141</v>
       </c>
-      <c r="B143" s="32" t="s">
-        <v>131</v>
+      <c r="B143" s="31" t="s">
+        <v>126</v>
       </c>
       <c r="C143" s="13">
         <v>-1</v>
@@ -8595,36 +8608,36 @@
         <v>392</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="K143" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L143" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"TG Tapering", </v>
       </c>
       <c r="M143" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N143" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_tapering, </v>
       </c>
       <c r="O143" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"TG Tapering", -1, -1, 392, NULL, tm_tapering, 0, 5, 0},  // Idx 141</v>
       </c>
       <c r="P143" s="6"/>
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>142</v>
       </c>
-      <c r="B144" s="32" t="s">
-        <v>132</v>
+      <c r="B144" s="31" t="s">
+        <v>127</v>
       </c>
       <c r="C144" s="13">
         <v>-1</v>
@@ -8646,36 +8659,36 @@
         <v>389</v>
       </c>
       <c r="J144" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K144" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L144" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"TG Flutter", </v>
       </c>
       <c r="M144" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N144" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O144" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"TG Flutter", -1, -1, 389, NULL, tm_pot, 0, 15, 0},  // Idx 142</v>
       </c>
       <c r="P144" s="6"/>
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>143</v>
       </c>
-      <c r="B145" s="32" t="s">
-        <v>133</v>
+      <c r="B145" s="31" t="s">
+        <v>128</v>
       </c>
       <c r="C145" s="13">
         <v>-1</v>
@@ -8697,36 +8710,36 @@
         <v>390</v>
       </c>
       <c r="J145" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K145" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L145" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"TG Leakage", </v>
       </c>
       <c r="M145" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N145" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O145" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"TG Leakage", -1, -1, 390, NULL, tm_pot, 0, 15, 0},  // Idx 143</v>
       </c>
       <c r="P145" s="6"/>
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>144</v>
       </c>
-      <c r="B146" s="32" t="s">
-        <v>153</v>
+      <c r="B146" s="31" t="s">
+        <v>148</v>
       </c>
       <c r="C146" s="13">
         <v>-1</v>
@@ -8748,36 +8761,36 @@
         <v>360</v>
       </c>
       <c r="J146" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K146" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L146" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Cont SpringFlx", </v>
       </c>
       <c r="M146" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N146" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O146" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Cont SpringFlx", -1, -1, 360, NULL, tm_pot, 0, 15, 0},  // Idx 144</v>
       </c>
       <c r="P146" s="6"/>
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>145</v>
       </c>
-      <c r="B147" s="32" t="s">
-        <v>154</v>
+      <c r="B147" s="31" t="s">
+        <v>149</v>
       </c>
       <c r="C147" s="13">
         <v>-1</v>
@@ -8799,36 +8812,36 @@
         <v>361</v>
       </c>
       <c r="J147" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K147" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L147" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Cont SpringDmp", </v>
       </c>
       <c r="M147" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N147" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O147" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Cont SpringDmp", -1, -1, 361, NULL, tm_pot, 0, 15, 0},  // Idx 145</v>
       </c>
       <c r="P147" s="6"/>
     </row>
     <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>146</v>
       </c>
-      <c r="B148" s="32" t="s">
-        <v>62</v>
+      <c r="B148" s="31" t="s">
+        <v>60</v>
       </c>
       <c r="C148" s="13">
         <v>-1</v>
@@ -8856,30 +8869,30 @@
         <v>8</v>
       </c>
       <c r="L148" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Lubed Contacts", </v>
       </c>
       <c r="M148" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N148" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O148" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Lubed Contacts", -1, -1, 364, NULL, tm_tab, 0, 1, 0},  // Idx 146</v>
       </c>
       <c r="P148" s="6"/>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>147</v>
       </c>
-      <c r="B149" s="32" t="s">
-        <v>134</v>
+      <c r="B149" s="31" t="s">
+        <v>129</v>
       </c>
       <c r="C149" s="13">
         <v>-1</v>
@@ -8907,30 +8920,30 @@
         <v>8</v>
       </c>
       <c r="L149" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"No DB1 @Perc", </v>
       </c>
       <c r="M149" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N149" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O149" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"No DB1 @Perc", -1, -1, 357, NULL, tm_tab, 0, 1, 0},  // Idx 147</v>
       </c>
       <c r="P149" s="6"/>
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>148</v>
       </c>
-      <c r="B150" s="32" t="s">
-        <v>161</v>
+      <c r="B150" s="31" t="s">
+        <v>156</v>
       </c>
       <c r="C150" s="13">
         <v>-1</v>
@@ -8952,36 +8965,36 @@
         <v>480</v>
       </c>
       <c r="J150" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K150" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L150" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Perc Norm Level", </v>
       </c>
       <c r="M150" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N150" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O150" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Perc Norm Level", -1, -1, 480, NULL, tm_pot, 0, 127, 0},  // Idx 148</v>
       </c>
       <c r="P150" s="6"/>
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A151" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>149</v>
       </c>
-      <c r="B151" s="32" t="s">
-        <v>162</v>
+      <c r="B151" s="31" t="s">
+        <v>157</v>
       </c>
       <c r="C151" s="13">
         <v>-1</v>
@@ -9003,36 +9016,36 @@
         <v>481</v>
       </c>
       <c r="J151" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K151" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L151" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Perc Soft Level", </v>
       </c>
       <c r="M151" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N151" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O151" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Perc Soft Level", -1, -1, 481, NULL, tm_pot, 0, 127, 0},  // Idx 149</v>
       </c>
       <c r="P151" s="6"/>
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>150</v>
       </c>
-      <c r="B152" s="32" t="s">
-        <v>135</v>
+      <c r="B152" s="31" t="s">
+        <v>130</v>
       </c>
       <c r="C152" s="13">
         <v>-1</v>
@@ -9054,36 +9067,36 @@
         <v>482</v>
       </c>
       <c r="J152" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K152" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L152" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Perc Long Time", </v>
       </c>
       <c r="M152" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N152" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O152" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Perc Long Time", -1, -1, 482, NULL, tm_pot, 0, 127, 0},  // Idx 150</v>
       </c>
       <c r="P152" s="6"/>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>151</v>
       </c>
-      <c r="B153" s="32" t="s">
-        <v>136</v>
+      <c r="B153" s="31" t="s">
+        <v>131</v>
       </c>
       <c r="C153" s="13">
         <v>-1</v>
@@ -9105,36 +9118,36 @@
         <v>483</v>
       </c>
       <c r="J153" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K153" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L153" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Perc Short Time", </v>
       </c>
       <c r="M153" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N153" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O153" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Perc Short Time", -1, -1, 483, NULL, tm_pot, 0, 127, 0},  // Idx 151</v>
       </c>
       <c r="P153" s="6"/>
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>152</v>
       </c>
-      <c r="B154" s="32" t="s">
-        <v>63</v>
+      <c r="B154" s="31" t="s">
+        <v>61</v>
       </c>
       <c r="C154" s="13">
         <v>-1</v>
@@ -9156,36 +9169,36 @@
         <v>484</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K154" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L154" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Perc Muted Lvl", </v>
       </c>
       <c r="M154" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N154" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O154" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Perc Muted Lvl", -1, -1, 484, NULL, tm_pot, 0, 127, 0},  // Idx 152</v>
       </c>
       <c r="P154" s="6"/>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A155" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>153</v>
       </c>
-      <c r="B155" s="32" t="s">
-        <v>54</v>
+      <c r="B155" s="31" t="s">
+        <v>52</v>
       </c>
       <c r="C155" s="13">
         <v>-1</v>
@@ -9207,36 +9220,36 @@
         <v>87</v>
       </c>
       <c r="J155" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K155" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L155" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"AO28 Tone Pot", </v>
       </c>
       <c r="M155" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N155" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O155" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"AO28 Tone Pot", -1, -1, 87, NULL, tm_pot, 0, 127, 0},  // Idx 153</v>
       </c>
       <c r="P155" s="6"/>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>154</v>
       </c>
-      <c r="B156" s="32" t="s">
-        <v>55</v>
+      <c r="B156" s="31" t="s">
+        <v>53</v>
       </c>
       <c r="C156" s="13">
         <v>-1</v>
@@ -9258,36 +9271,36 @@
         <v>88</v>
       </c>
       <c r="J156" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K156" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L156" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"AO28 Gain Cap", </v>
       </c>
       <c r="M156" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N156" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O156" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"AO28 Gain Cap", -1, -1, 88, NULL, tm_pot, 0, 127, 0},  // Idx 154</v>
       </c>
       <c r="P156" s="6"/>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>155</v>
       </c>
-      <c r="B157" s="32" t="s">
-        <v>56</v>
+      <c r="B157" s="31" t="s">
+        <v>54</v>
       </c>
       <c r="C157" s="13">
         <v>-1</v>
@@ -9309,36 +9322,36 @@
         <v>89</v>
       </c>
       <c r="J157" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K157" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L157" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"AO28 MinSwell", </v>
       </c>
       <c r="M157" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N157" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O157" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"AO28 MinSwell", -1, -1, 89, NULL, tm_pot, 0, 127, 0},  // Idx 155</v>
       </c>
       <c r="P157" s="6"/>
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>156</v>
       </c>
-      <c r="B158" s="32" t="s">
-        <v>57</v>
+      <c r="B158" s="31" t="s">
+        <v>55</v>
       </c>
       <c r="C158" s="13">
         <v>-1</v>
@@ -9360,36 +9373,36 @@
         <v>90</v>
       </c>
       <c r="J158" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K158" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L158" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"AO28 Tube Age", </v>
       </c>
       <c r="M158" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N158" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O158" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"AO28 Tube Age", -1, -1, 90, NULL, tm_pot, 0, 127, 0},  // Idx 156</v>
       </c>
       <c r="P158" s="6"/>
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>157</v>
       </c>
-      <c r="B159" s="32" t="s">
-        <v>192</v>
+      <c r="B159" s="31" t="s">
+        <v>186</v>
       </c>
       <c r="C159" s="13">
         <v>-1</v>
@@ -9411,36 +9424,36 @@
         <v>82</v>
       </c>
       <c r="J159" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K159" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L159" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Upper Level", </v>
       </c>
       <c r="M159" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N159" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O159" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Upper Level", -1, -1, 82, NULL, tm_pot, 0, 127, 0},  // Idx 157</v>
       </c>
       <c r="P159" s="6"/>
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>158</v>
       </c>
-      <c r="B160" s="32" t="s">
-        <v>193</v>
+      <c r="B160" s="31" t="s">
+        <v>187</v>
       </c>
       <c r="C160" s="13">
         <v>-1</v>
@@ -9462,36 +9475,36 @@
         <v>83</v>
       </c>
       <c r="J160" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K160" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L160" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Lower Level", </v>
       </c>
       <c r="M160" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N160" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O160" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Lower Level", -1, -1, 83, NULL, tm_pot, 0, 127, 0},  // Idx 158</v>
       </c>
       <c r="P160" s="6"/>
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>159</v>
       </c>
-      <c r="B161" s="32" t="s">
-        <v>194</v>
+      <c r="B161" s="31" t="s">
+        <v>188</v>
       </c>
       <c r="C161" s="13">
         <v>-1</v>
@@ -9513,36 +9526,36 @@
         <v>84</v>
       </c>
       <c r="J161" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K161" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L161" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Pedal Level", </v>
       </c>
       <c r="M161" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N161" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O161" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Pedal Level", -1, -1, 84, NULL, tm_pot, 0, 127, 0},  // Idx 159</v>
       </c>
       <c r="P161" s="6"/>
     </row>
     <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>160</v>
       </c>
-      <c r="B162" s="32" t="s">
-        <v>195</v>
+      <c r="B162" s="31" t="s">
+        <v>189</v>
       </c>
       <c r="C162" s="13">
         <v>-1</v>
@@ -9564,36 +9577,36 @@
         <v>85</v>
       </c>
       <c r="J162" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K162" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L162" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Perc Level", </v>
       </c>
       <c r="M162" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N162" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O162" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Perc Level", -1, -1, 85, NULL, tm_pot, 0, 127, 0},  // Idx 160</v>
       </c>
       <c r="P162" s="6"/>
     </row>
     <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>161</v>
       </c>
-      <c r="B163" s="36" t="s">
-        <v>163</v>
+      <c r="B163" s="34" t="s">
+        <v>158</v>
       </c>
       <c r="C163" s="13">
         <v>-1</v>
@@ -9615,36 +9628,36 @@
         <v>400</v>
       </c>
       <c r="J163" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K163" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L163" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Reverb 1 Level ", </v>
       </c>
       <c r="M163" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N163" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O163" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Reverb 1 Level ", -1, -1, 400, NULL, tm_pot, 0, 127, 0},  // Idx 161</v>
       </c>
       <c r="P163" s="6"/>
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>162</v>
       </c>
-      <c r="B164" s="36" t="s">
-        <v>164</v>
+      <c r="B164" s="34" t="s">
+        <v>159</v>
       </c>
       <c r="C164" s="13">
         <v>-1</v>
@@ -9666,36 +9679,36 @@
         <v>401</v>
       </c>
       <c r="J164" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K164" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L164" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Reverb 2 Level ", </v>
       </c>
       <c r="M164" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N164" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O164" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Reverb 2 Level ", -1, -1, 401, NULL, tm_pot, 0, 127, 0},  // Idx 162</v>
       </c>
       <c r="P164" s="6"/>
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>163</v>
       </c>
-      <c r="B165" s="36" t="s">
-        <v>165</v>
+      <c r="B165" s="34" t="s">
+        <v>160</v>
       </c>
       <c r="C165" s="13">
         <v>-1</v>
@@ -9717,36 +9730,36 @@
         <v>402</v>
       </c>
       <c r="J165" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K165" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L165" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Reverb 3 Level ", </v>
       </c>
       <c r="M165" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N165" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O165" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Reverb 3 Level ", -1, -1, 402, NULL, tm_pot, 0, 127, 0},  // Idx 163</v>
       </c>
       <c r="P165" s="6"/>
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>164</v>
       </c>
-      <c r="B166" s="33" t="s">
-        <v>137</v>
+      <c r="B166" s="32" t="s">
+        <v>132</v>
       </c>
       <c r="C166" s="13">
         <v>-1</v>
@@ -9774,30 +9787,30 @@
         <v>8</v>
       </c>
       <c r="L166" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Bypass", </v>
       </c>
       <c r="M166" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N166" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O166" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Bypass", -1, -1, 159, NULL, tm_tab, 0, 1, 0},  // Idx 164</v>
       </c>
       <c r="P166" s="6"/>
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>165</v>
       </c>
-      <c r="B167" s="33" t="s">
-        <v>138</v>
+      <c r="B167" s="32" t="s">
+        <v>133</v>
       </c>
       <c r="C167" s="13">
         <v>-1</v>
@@ -9819,36 +9832,36 @@
         <v>112</v>
       </c>
       <c r="J167" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K167" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L167" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Bass Level", </v>
       </c>
       <c r="M167" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N167" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O167" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Bass Level", -1, -1, 112, NULL, tm_pot, 0, 127, 0},  // Idx 165</v>
       </c>
       <c r="P167" s="6"/>
     </row>
     <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>166</v>
       </c>
-      <c r="B168" s="33" t="s">
-        <v>139</v>
+      <c r="B168" s="32" t="s">
+        <v>134</v>
       </c>
       <c r="C168" s="13">
         <v>-1</v>
@@ -9870,36 +9883,36 @@
         <v>113</v>
       </c>
       <c r="J168" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K168" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L168" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Bass Equ Frq", </v>
       </c>
       <c r="M168" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N168" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O168" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Bass Equ Frq", -1, -1, 113, NULL, tm_pot, 0, 127, 0},  // Idx 166</v>
       </c>
       <c r="P168" s="6"/>
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>167</v>
       </c>
-      <c r="B169" s="33" t="s">
-        <v>142</v>
+      <c r="B169" s="32" t="s">
+        <v>137</v>
       </c>
       <c r="C169" s="13">
         <v>-1</v>
@@ -9921,36 +9934,36 @@
         <v>114</v>
       </c>
       <c r="J169" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K169" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L169" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Bass Equ Q", </v>
       </c>
       <c r="M169" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N169" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O169" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Bass Equ Q", -1, -1, 114, NULL, tm_pot, 0, 127, 0},  // Idx 167</v>
       </c>
       <c r="P169" s="6"/>
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>168</v>
       </c>
-      <c r="B170" s="33" t="s">
-        <v>140</v>
+      <c r="B170" s="32" t="s">
+        <v>135</v>
       </c>
       <c r="C170" s="13">
         <v>-1</v>
@@ -9972,36 +9985,36 @@
         <v>115</v>
       </c>
       <c r="J170" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K170" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L170" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Mid Level", </v>
       </c>
       <c r="M170" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N170" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O170" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Mid Level", -1, -1, 115, NULL, tm_pot, 0, 127, 0},  // Idx 168</v>
       </c>
       <c r="P170" s="6"/>
     </row>
     <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>169</v>
       </c>
-      <c r="B171" s="33" t="s">
-        <v>52</v>
+      <c r="B171" s="32" t="s">
+        <v>50</v>
       </c>
       <c r="C171" s="13">
         <v>-1</v>
@@ -10023,36 +10036,36 @@
         <v>116</v>
       </c>
       <c r="J171" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K171" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L171" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Mid Equ Frq  ", </v>
       </c>
       <c r="M171" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N171" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O171" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Mid Equ Frq  ", -1, -1, 116, NULL, tm_pot, 0, 127, 0},  // Idx 169</v>
       </c>
       <c r="P171" s="6"/>
     </row>
     <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>170</v>
       </c>
-      <c r="B172" s="33" t="s">
-        <v>141</v>
+      <c r="B172" s="32" t="s">
+        <v>136</v>
       </c>
       <c r="C172" s="13">
         <v>-1</v>
@@ -10074,36 +10087,36 @@
         <v>117</v>
       </c>
       <c r="J172" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K172" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L172" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Mid Equ Q", </v>
       </c>
       <c r="M172" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N172" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O172" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v xml:space="preserve">  {"Mid Equ Q", -1, -1, 117, NULL, tm_pot, 0, 127, 0},  // Idx 170</v>
       </c>
       <c r="P172" s="6"/>
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>171</v>
       </c>
-      <c r="B173" s="33" t="s">
-        <v>128</v>
+      <c r="B173" s="32" t="s">
+        <v>123</v>
       </c>
       <c r="C173" s="13">
         <v>-1</v>
@@ -10125,36 +10138,36 @@
         <v>118</v>
       </c>
       <c r="J173" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K173" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L173" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Treble Level", </v>
       </c>
       <c r="M173" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N173" s="11" t="str">
-        <f t="shared" ref="N173:N206" si="48">IF(J173="NULL",CONCATENATE(J173,", "),CONCATENATE("tm_",J173,", "))</f>
+        <f t="shared" ref="N173:N207" si="49">IF(J173="NULL",CONCATENATE(J173,", "),CONCATENATE("tm_",J173,", "))</f>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O173" s="10" t="str">
-        <f t="shared" ref="O173:O204" si="49">CONCATENATE("  {",L173,C173,", ",D173,", ",I173,", ",M173,N173,F173,", ",G173,", ",H173,"},  // Idx ", A173)</f>
+        <f t="shared" ref="O173:O204" si="50">CONCATENATE("  {",L173,C173,", ",D173,", ",I173,", ",M173,N173,F173,", ",G173,", ",H173,"},  // Idx ", A173)</f>
         <v xml:space="preserve">  {"Treble Level", -1, -1, 118, NULL, tm_pot, 0, 127, 0},  // Idx 171</v>
       </c>
       <c r="P173" s="6"/>
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>172</v>
       </c>
-      <c r="B174" s="33" t="s">
-        <v>145</v>
+      <c r="B174" s="32" t="s">
+        <v>140</v>
       </c>
       <c r="C174" s="13">
         <v>-1</v>
@@ -10176,36 +10189,36 @@
         <v>119</v>
       </c>
       <c r="J174" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K174" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L174" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Treb Equ Frq", </v>
       </c>
       <c r="M174" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N174" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O174" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"Treb Equ Frq", -1, -1, 119, NULL, tm_pot, 0, 127, 0},  // Idx 172</v>
       </c>
       <c r="P174" s="6"/>
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>173</v>
       </c>
-      <c r="B175" s="33" t="s">
-        <v>144</v>
+      <c r="B175" s="32" t="s">
+        <v>139</v>
       </c>
       <c r="C175" s="13">
         <v>-1</v>
@@ -10227,36 +10240,36 @@
         <v>120</v>
       </c>
       <c r="J175" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K175" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L175" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Treb Equ Q", </v>
       </c>
       <c r="M175" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N175" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O175" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"Treb Equ Q", -1, -1, 120, NULL, tm_pot, 0, 127, 0},  // Idx 173</v>
       </c>
       <c r="P175" s="6"/>
     </row>
     <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>174</v>
       </c>
-      <c r="B176" s="33" t="s">
-        <v>143</v>
+      <c r="B176" s="32" t="s">
+        <v>138</v>
       </c>
       <c r="C176" s="13">
         <v>-1</v>
@@ -10284,30 +10297,30 @@
         <v>8</v>
       </c>
       <c r="L176" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">"Parametr B/T", </v>
       </c>
       <c r="M176" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N176" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_tab, </v>
       </c>
       <c r="O176" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"Parametr B/T", -1, -1, 121, NULL, tm_tab, 0, 1, 0},  // Idx 174</v>
       </c>
       <c r="P176" s="6"/>
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>175</v>
       </c>
-      <c r="B177" s="31" t="s">
-        <v>120</v>
+      <c r="B177" s="30" t="s">
+        <v>115</v>
       </c>
       <c r="C177" s="13">
         <v>-1</v>
@@ -10329,36 +10342,36 @@
         <v>448</v>
       </c>
       <c r="J177" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K177" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L177" s="11" t="str">
-        <f t="shared" ref="L177:L184" si="50">CONCATENATE("""",B177,""", ")</f>
+        <f t="shared" ref="L177:L184" si="51">CONCATENATE("""",B177,""", ")</f>
         <v xml:space="preserve">"Horn SlowSpeed", </v>
       </c>
       <c r="M177" s="11" t="str">
-        <f t="shared" ref="M177:M184" si="51">IF(K177="NULL",CONCATENATE(K177,", "),CONCATENATE("&amp;",K177,", "))</f>
+        <f t="shared" ref="M177:M184" si="52">IF(K177="NULL",CONCATENATE(K177,", "),CONCATENATE("&amp;",K177,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N177" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O177" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"Horn SlowSpeed", -1, -1, 448, NULL, tm_pot, 0, 63, 0},  // Idx 175</v>
       </c>
       <c r="P177" s="6"/>
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>176</v>
       </c>
-      <c r="B178" s="31" t="s">
-        <v>121</v>
+      <c r="B178" s="30" t="s">
+        <v>116</v>
       </c>
       <c r="C178" s="13">
         <v>-1</v>
@@ -10380,36 +10393,36 @@
         <v>449</v>
       </c>
       <c r="J178" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K178" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L178" s="11" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">"Rotr SlowSpeed", </v>
+      </c>
+      <c r="M178" s="11" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N178" s="11" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O178" s="10" t="str">
         <f t="shared" si="50"/>
-        <v xml:space="preserve">"Rotr SlowSpeed", </v>
-      </c>
-      <c r="M178" s="11" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N178" s="11" t="str">
-        <f t="shared" si="48"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O178" s="10" t="str">
-        <f t="shared" si="49"/>
         <v xml:space="preserve">  {"Rotr SlowSpeed", -1, -1, 449, NULL, tm_pot, 0, 63, 0},  // Idx 176</v>
       </c>
       <c r="P178" s="6"/>
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>177</v>
       </c>
-      <c r="B179" s="31" t="s">
-        <v>122</v>
+      <c r="B179" s="30" t="s">
+        <v>117</v>
       </c>
       <c r="C179" s="13">
         <v>-1</v>
@@ -10431,36 +10444,36 @@
         <v>450</v>
       </c>
       <c r="J179" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K179" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L179" s="11" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">"Horn FastSpeed", </v>
+      </c>
+      <c r="M179" s="11" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N179" s="11" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O179" s="10" t="str">
         <f t="shared" si="50"/>
-        <v xml:space="preserve">"Horn FastSpeed", </v>
-      </c>
-      <c r="M179" s="11" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N179" s="11" t="str">
-        <f t="shared" si="48"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O179" s="10" t="str">
-        <f t="shared" si="49"/>
         <v xml:space="preserve">  {"Horn FastSpeed", -1, -1, 450, NULL, tm_pot, 0, 127, 0},  // Idx 177</v>
       </c>
       <c r="P179" s="6"/>
     </row>
     <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>178</v>
       </c>
-      <c r="B180" s="31" t="s">
-        <v>123</v>
+      <c r="B180" s="30" t="s">
+        <v>118</v>
       </c>
       <c r="C180" s="13">
         <v>-1</v>
@@ -10482,36 +10495,36 @@
         <v>451</v>
       </c>
       <c r="J180" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K180" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L180" s="11" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">"Rotr FastSpeed", </v>
+      </c>
+      <c r="M180" s="11" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N180" s="11" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O180" s="10" t="str">
         <f t="shared" si="50"/>
-        <v xml:space="preserve">"Rotr FastSpeed", </v>
-      </c>
-      <c r="M180" s="11" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N180" s="11" t="str">
-        <f t="shared" si="48"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O180" s="10" t="str">
-        <f t="shared" si="49"/>
         <v xml:space="preserve">  {"Rotr FastSpeed", -1, -1, 451, NULL, tm_pot, 0, 127, 0},  // Idx 178</v>
       </c>
       <c r="P180" s="6"/>
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>179</v>
       </c>
-      <c r="B181" s="31" t="s">
-        <v>124</v>
+      <c r="B181" s="30" t="s">
+        <v>119</v>
       </c>
       <c r="C181" s="13">
         <v>-1</v>
@@ -10533,36 +10546,36 @@
         <v>452</v>
       </c>
       <c r="J181" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K181" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L181" s="11" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">"Horn RampUp   ", </v>
+      </c>
+      <c r="M181" s="11" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N181" s="11" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O181" s="10" t="str">
         <f t="shared" si="50"/>
-        <v xml:space="preserve">"Horn RampUp   ", </v>
-      </c>
-      <c r="M181" s="11" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N181" s="11" t="str">
-        <f t="shared" si="48"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O181" s="10" t="str">
-        <f t="shared" si="49"/>
         <v xml:space="preserve">  {"Horn RampUp   ", -1, -1, 452, NULL, tm_pot, 0, 31, 0},  // Idx 179</v>
       </c>
       <c r="P181" s="6"/>
     </row>
     <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>180</v>
       </c>
-      <c r="B182" s="31" t="s">
-        <v>125</v>
+      <c r="B182" s="30" t="s">
+        <v>120</v>
       </c>
       <c r="C182" s="13">
         <v>-1</v>
@@ -10584,36 +10597,36 @@
         <v>453</v>
       </c>
       <c r="J182" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K182" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L182" s="11" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">"Rotor RampUp  ", </v>
+      </c>
+      <c r="M182" s="11" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N182" s="11" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O182" s="10" t="str">
         <f t="shared" si="50"/>
-        <v xml:space="preserve">"Rotor RampUp  ", </v>
-      </c>
-      <c r="M182" s="11" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N182" s="11" t="str">
-        <f t="shared" si="48"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O182" s="10" t="str">
-        <f t="shared" si="49"/>
         <v xml:space="preserve">  {"Rotor RampUp  ", -1, -1, 453, NULL, tm_pot, 0, 31, 0},  // Idx 180</v>
       </c>
       <c r="P182" s="6"/>
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>181</v>
       </c>
-      <c r="B183" s="31" t="s">
-        <v>126</v>
+      <c r="B183" s="30" t="s">
+        <v>121</v>
       </c>
       <c r="C183" s="13">
         <v>-1</v>
@@ -10635,36 +10648,36 @@
         <v>454</v>
       </c>
       <c r="J183" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K183" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L183" s="11" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">"Horn RampDown ", </v>
+      </c>
+      <c r="M183" s="11" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N183" s="11" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O183" s="10" t="str">
         <f t="shared" si="50"/>
-        <v xml:space="preserve">"Horn RampDown ", </v>
-      </c>
-      <c r="M183" s="11" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N183" s="11" t="str">
-        <f t="shared" si="48"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O183" s="10" t="str">
-        <f t="shared" si="49"/>
         <v xml:space="preserve">  {"Horn RampDown ", -1, -1, 454, NULL, tm_pot, 0, 31, 0},  // Idx 181</v>
       </c>
       <c r="P183" s="6"/>
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>182</v>
       </c>
-      <c r="B184" s="31" t="s">
-        <v>127</v>
+      <c r="B184" s="30" t="s">
+        <v>122</v>
       </c>
       <c r="C184" s="13">
         <v>-1</v>
@@ -10686,36 +10699,36 @@
         <v>455</v>
       </c>
       <c r="J184" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K184" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L184" s="11" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">"Rotor RampDown", </v>
+      </c>
+      <c r="M184" s="11" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="N184" s="11" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">tm_pot, </v>
+      </c>
+      <c r="O184" s="10" t="str">
         <f t="shared" si="50"/>
-        <v xml:space="preserve">"Rotor RampDown", </v>
-      </c>
-      <c r="M184" s="11" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="N184" s="11" t="str">
-        <f t="shared" si="48"/>
-        <v xml:space="preserve">tm_pot, </v>
-      </c>
-      <c r="O184" s="10" t="str">
-        <f t="shared" si="49"/>
         <v xml:space="preserve">  {"Rotor RampDown", -1, -1, 455, NULL, tm_pot, 0, 31, 0},  // Idx 182</v>
       </c>
       <c r="P184" s="6"/>
     </row>
     <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>183</v>
       </c>
-      <c r="B185" s="31" t="s">
-        <v>58</v>
+      <c r="B185" s="30" t="s">
+        <v>56</v>
       </c>
       <c r="C185" s="13">
         <v>-1</v>
@@ -10737,36 +10750,36 @@
         <v>456</v>
       </c>
       <c r="J185" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K185" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L185" s="11" t="str">
-        <f t="shared" ref="L185:L206" si="52">CONCATENATE("""",B185,""", ")</f>
+        <f t="shared" ref="L185:L207" si="53">CONCATENATE("""",B185,""", ")</f>
         <v xml:space="preserve">"Rotary Throb ", </v>
       </c>
       <c r="M185" s="11" t="str">
-        <f t="shared" ref="M185:M206" si="53">IF(K185="NULL",CONCATENATE(K185,", "),CONCATENATE("&amp;",K185,", "))</f>
+        <f t="shared" ref="M185:M207" si="54">IF(K185="NULL",CONCATENATE(K185,", "),CONCATENATE("&amp;",K185,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N185" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O185" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"Rotary Throb ", -1, -1, 456, NULL, tm_pot, 0, 127, 0},  // Idx 183</v>
       </c>
       <c r="P185" s="6"/>
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>184</v>
       </c>
-      <c r="B186" s="31" t="s">
-        <v>59</v>
+      <c r="B186" s="30" t="s">
+        <v>57</v>
       </c>
       <c r="C186" s="13">
         <v>-1</v>
@@ -10788,36 +10801,36 @@
         <v>457</v>
       </c>
       <c r="J186" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K186" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L186" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"Rotary Spread", </v>
       </c>
       <c r="M186" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N186" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O186" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"Rotary Spread", -1, -1, 457, NULL, tm_pot, 0, 127, 0},  // Idx 184</v>
       </c>
       <c r="P186" s="6"/>
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>185</v>
       </c>
-      <c r="B187" s="31" t="s">
-        <v>166</v>
+      <c r="B187" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="C187" s="13">
         <v>-1</v>
@@ -10839,36 +10852,36 @@
         <v>458</v>
       </c>
       <c r="J187" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K187" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L187" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"Rotary Balance", </v>
       </c>
       <c r="M187" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N187" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O187" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"Rotary Balance", -1, -1, 458, NULL, tm_pot, 0, 127, 0},  // Idx 185</v>
       </c>
       <c r="P187" s="6"/>
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>186</v>
       </c>
-      <c r="B188" s="31" t="s">
-        <v>60</v>
+      <c r="B188" s="30" t="s">
+        <v>58</v>
       </c>
       <c r="C188" s="13">
         <v>-1</v>
@@ -10896,30 +10909,30 @@
         <v>8</v>
       </c>
       <c r="L188" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"Tube Select A", </v>
       </c>
       <c r="M188" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N188" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O188" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"Tube Select A", -1, -1, 460, NULL, tm_numeric, 0, 7, 0},  // Idx 186</v>
       </c>
       <c r="P188" s="6"/>
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>187</v>
       </c>
-      <c r="B189" s="31" t="s">
-        <v>61</v>
+      <c r="B189" s="30" t="s">
+        <v>59</v>
       </c>
       <c r="C189" s="13">
         <v>-1</v>
@@ -10947,30 +10960,30 @@
         <v>8</v>
       </c>
       <c r="L189" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"Tube Select B", </v>
       </c>
       <c r="M189" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N189" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O189" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"Tube Select B", -1, -1, 461, NULL, tm_numeric, 0, 7, 0},  // Idx 187</v>
       </c>
       <c r="P189" s="6"/>
     </row>
     <row r="190" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>188</v>
       </c>
-      <c r="B190" s="35" t="s">
-        <v>45</v>
+      <c r="B190" s="33" t="s">
+        <v>43</v>
       </c>
       <c r="C190" s="13">
         <v>-1</v>
@@ -10998,28 +11011,28 @@
         <v>8</v>
       </c>
       <c r="L190" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"Transpose", </v>
       </c>
       <c r="M190" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N190" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O190" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"Transpose", -1, -1, 355, NULL, tm_numeric, 0, 24, 0},  // Idx 188</v>
       </c>
     </row>
     <row r="191" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>189</v>
       </c>
-      <c r="B191" s="35" t="s">
+      <c r="B191" s="33" t="s">
         <v>1</v>
       </c>
       <c r="C191" s="13">
@@ -11042,34 +11055,34 @@
         <v>363</v>
       </c>
       <c r="J191" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K191" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L191" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"Velocity Slope", </v>
       </c>
       <c r="M191" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N191" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O191" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"Velocity Slope", -1, -1, 363, NULL, tm_pot, 1, 30, 0},  // Idx 189</v>
       </c>
     </row>
     <row r="192" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>190</v>
       </c>
-      <c r="B192" s="35" t="s">
+      <c r="B192" s="33" t="s">
         <v>11</v>
       </c>
       <c r="C192" s="13">
@@ -11080,10 +11093,10 @@
       </c>
       <c r="E192" s="13"/>
       <c r="F192" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G192" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H192" s="7">
         <v>0</v>
@@ -11092,35 +11105,35 @@
         <v>368</v>
       </c>
       <c r="J192" s="7" t="s">
-        <v>26</v>
+        <v>196</v>
       </c>
       <c r="K192" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L192" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"MIDI Channel", </v>
       </c>
       <c r="M192" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N192" s="11" t="str">
-        <f t="shared" si="48"/>
-        <v xml:space="preserve">tm_numeric, </v>
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">tm_midich, </v>
       </c>
       <c r="O192" s="10" t="str">
-        <f t="shared" si="49"/>
-        <v xml:space="preserve">  {"MIDI Channel", -1, -1, 368, NULL, tm_numeric, 1, 12, 0},  // Idx 190</v>
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">  {"MIDI Channel", -1, -1, 368, NULL, tm_midich, 0, 11, 0},  // Idx 190</v>
       </c>
     </row>
     <row r="193" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>191</v>
       </c>
-      <c r="B193" s="35" t="s">
-        <v>33</v>
+      <c r="B193" s="33" t="s">
+        <v>31</v>
       </c>
       <c r="C193" s="13">
         <v>-1</v>
@@ -11142,35 +11155,35 @@
         <v>370</v>
       </c>
       <c r="J193" s="7" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="K193" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L193" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"MIDI CC Set  ", </v>
       </c>
       <c r="M193" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N193" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_midicc, </v>
       </c>
       <c r="O193" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"MIDI CC Set  ", -1, -1, 370, NULL, tm_midicc, 0, 10, 0},  // Idx 191</v>
       </c>
     </row>
     <row r="194" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>192</v>
       </c>
-      <c r="B194" s="35" t="s">
-        <v>34</v>
+      <c r="B194" s="33" t="s">
+        <v>32</v>
       </c>
       <c r="C194" s="13">
         <v>-1</v>
@@ -11198,29 +11211,29 @@
         <v>8</v>
       </c>
       <c r="L194" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"MIDI Swell CC", </v>
       </c>
       <c r="M194" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N194" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O194" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"MIDI Swell CC", -1, -1, 371, NULL, tm_numeric, 0, 127, 0},  // Idx 192</v>
       </c>
     </row>
     <row r="195" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>193</v>
       </c>
-      <c r="B195" s="35" t="s">
-        <v>35</v>
+      <c r="B195" s="33" t="s">
+        <v>33</v>
       </c>
       <c r="C195" s="13">
         <v>-1</v>
@@ -11248,29 +11261,29 @@
         <v>8</v>
       </c>
       <c r="L195" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"MIDI VolumeCC", </v>
       </c>
       <c r="M195" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N195" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O195" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"MIDI VolumeCC", -1, -1, 372, NULL, tm_numeric, 0, 127, 0},  // Idx 193</v>
       </c>
     </row>
     <row r="196" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>194</v>
       </c>
-      <c r="B196" s="35" t="s">
-        <v>36</v>
+      <c r="B196" s="33" t="s">
+        <v>34</v>
       </c>
       <c r="C196" s="13">
         <v>-1</v>
@@ -11298,29 +11311,29 @@
         <v>8</v>
       </c>
       <c r="L196" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"MIDI PresetCC", </v>
       </c>
       <c r="M196" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N196" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O196" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"MIDI PresetCC", -1, -1, 374, NULL, tm_numeric, 0, 127, 0},  // Idx 194</v>
       </c>
     </row>
     <row r="197" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>195</v>
       </c>
-      <c r="B197" s="35" t="s">
-        <v>37</v>
+      <c r="B197" s="33" t="s">
+        <v>35</v>
       </c>
       <c r="C197" s="13">
         <v>-1</v>
@@ -11348,29 +11361,29 @@
         <v>8</v>
       </c>
       <c r="L197" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"MIDI Send    ", </v>
       </c>
       <c r="M197" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N197" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O197" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"MIDI Send    ", -1, -1, 373, NULL, tm_numeric, 0, 127, 0},  // Idx 195</v>
       </c>
     </row>
     <row r="198" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>196</v>
       </c>
-      <c r="B198" s="35" t="s">
-        <v>38</v>
+      <c r="B198" s="33" t="s">
+        <v>36</v>
       </c>
       <c r="C198" s="13">
         <v>-1</v>
@@ -11398,29 +11411,29 @@
         <v>8</v>
       </c>
       <c r="L198" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"Split Keyb   ", </v>
       </c>
       <c r="M198" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N198" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O198" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"Split Keyb   ", -1, -1, 143, NULL, tm_numeric, 0, 127, 0},  // Idx 196</v>
       </c>
     </row>
     <row r="199" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>197</v>
       </c>
-      <c r="B199" s="35" t="s">
-        <v>39</v>
+      <c r="B199" s="33" t="s">
+        <v>37</v>
       </c>
       <c r="C199" s="13">
         <v>-1</v>
@@ -11448,29 +11461,29 @@
         <v>8</v>
       </c>
       <c r="L199" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"Split Point  ", </v>
       </c>
       <c r="M199" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N199" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O199" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"Split Point  ", -1, -1, 353, NULL, tm_numeric, 0, 127, 0},  // Idx 197</v>
       </c>
     </row>
     <row r="200" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>198</v>
       </c>
-      <c r="B200" s="35" t="s">
-        <v>40</v>
+      <c r="B200" s="33" t="s">
+        <v>38</v>
       </c>
       <c r="C200" s="13">
         <v>-1</v>
@@ -11498,29 +11511,29 @@
         <v>8</v>
       </c>
       <c r="L200" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"Split Mode   ", </v>
       </c>
       <c r="M200" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N200" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O200" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"Split Mode   ", -1, -1, 354, NULL, tm_numeric, 0, 5, 0},  // Idx 198</v>
       </c>
     </row>
     <row r="201" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>199</v>
       </c>
-      <c r="B201" s="35" t="s">
-        <v>41</v>
+      <c r="B201" s="33" t="s">
+        <v>39</v>
       </c>
       <c r="C201" s="13">
         <v>-1</v>
@@ -11548,29 +11561,29 @@
         <v>8</v>
       </c>
       <c r="L201" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"No ProgChgRcv", </v>
       </c>
       <c r="M201" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N201" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_numeric, </v>
       </c>
       <c r="O201" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v xml:space="preserve">  {"No ProgChgRcv", -1, -1, 376, NULL, tm_numeric, 0, 127, 0},  // Idx 199</v>
       </c>
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202" s="16">
-        <f t="shared" ref="A202:A205" si="54">A201+1</f>
+        <f t="shared" ref="A202:A206" si="55">A201+1</f>
         <v>200</v>
       </c>
-      <c r="B202" s="34" t="s">
-        <v>179</v>
+      <c r="B202" s="44" t="s">
+        <v>192</v>
       </c>
       <c r="C202" s="13">
         <v>-1</v>
@@ -11592,35 +11605,35 @@
         <v>-1</v>
       </c>
       <c r="J202" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K202" s="7" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="L202" s="11" t="str">
-        <f t="shared" si="52"/>
-        <v xml:space="preserve">"Preset Name  ", </v>
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">"Preset Name", </v>
       </c>
       <c r="M202" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">&amp;enterPresetName, </v>
       </c>
       <c r="N202" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_button, </v>
       </c>
       <c r="O202" s="10" t="str">
-        <f t="shared" si="49"/>
-        <v xml:space="preserve">  {"Preset Name  ", -1, -1, -1, &amp;enterPresetName, tm_button, 0, 1, 0},  // Idx 200</v>
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">  {"Preset Name", -1, -1, -1, &amp;enterPresetName, tm_button, 0, 1, 0},  // Idx 200</v>
       </c>
     </row>
     <row r="203" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A203" s="16">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>201</v>
       </c>
-      <c r="B203" s="34" t="s">
-        <v>32</v>
+      <c r="B203" s="44" t="s">
+        <v>191</v>
       </c>
       <c r="C203" s="13">
         <v>-1</v>
@@ -11642,35 +11655,35 @@
         <v>-1</v>
       </c>
       <c r="J203" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K203" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L203" s="11" t="str">
-        <f t="shared" si="52"/>
-        <v xml:space="preserve">"Preset Init  ", </v>
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">"Preset Init", </v>
       </c>
       <c r="M203" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N203" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_button, </v>
       </c>
       <c r="O203" s="10" t="str">
-        <f t="shared" si="49"/>
-        <v xml:space="preserve">  {"Preset Init  ", -1, -1, -1, NULL, tm_button, 0, 1, 0},  // Idx 201</v>
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">  {"Preset Init", -1, -1, -1, NULL, tm_button, 0, 1, 0},  // Idx 201</v>
       </c>
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204" s="16">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>202</v>
       </c>
-      <c r="B204" s="34" t="s">
-        <v>30</v>
+      <c r="B204" s="45" t="s">
+        <v>198</v>
       </c>
       <c r="C204" s="13">
         <v>-1</v>
@@ -11692,35 +11705,35 @@
         <v>495</v>
       </c>
       <c r="J204" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K204" s="7" t="s">
         <v>8</v>
       </c>
       <c r="L204" s="11" t="str">
-        <f t="shared" si="52"/>
-        <v xml:space="preserve">"LED Dimmer   ", </v>
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">"LED Dimmer", </v>
       </c>
       <c r="M204" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="N204" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_pot, </v>
       </c>
       <c r="O204" s="10" t="str">
-        <f t="shared" si="49"/>
-        <v xml:space="preserve">  {"LED Dimmer   ", -1, -1, 495, NULL, tm_pot, 0, 15, 0},  // Idx 202</v>
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">  {"LED Dimmer", -1, -1, 495, NULL, tm_pot, 0, 15, 0},  // Idx 202</v>
       </c>
     </row>
     <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A205" s="16">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>203</v>
       </c>
-      <c r="B205" s="34" t="s">
-        <v>31</v>
+      <c r="B205" s="45" t="s">
+        <v>199</v>
       </c>
       <c r="C205" s="13">
         <v>-1</v>
@@ -11733,100 +11746,150 @@
         <v>0</v>
       </c>
       <c r="G205" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H205" s="7">
         <v>0</v>
       </c>
       <c r="I205" s="18">
-        <v>-1</v>
+        <v>499</v>
       </c>
       <c r="J205" s="7" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="K205" s="7" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="L205" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" ref="L205" si="56">CONCATENATE("""",B205,""", ")</f>
+        <v xml:space="preserve">"Screen Saver", </v>
+      </c>
+      <c r="M205" s="11" t="str">
+        <f t="shared" ref="M205" si="57">IF(K205="NULL",CONCATENATE(K205,", "),CONCATENATE("&amp;",K205,", "))</f>
+        <v xml:space="preserve">&amp;enterScreenSaver, </v>
+      </c>
+      <c r="N205" s="11" t="str">
+        <f t="shared" ref="N205" si="58">IF(J205="NULL",CONCATENATE(J205,", "),CONCATENATE("tm_",J205,", "))</f>
+        <v xml:space="preserve">tm_numeric, </v>
+      </c>
+      <c r="O205" s="10" t="str">
+        <f t="shared" ref="O205" si="59">CONCATENATE("  {",L205,C205,", ",D205,", ",I205,", ",M205,N205,F205,", ",G205,", ",H205,"},  // Idx ", A205)</f>
+        <v xml:space="preserve">  {"Screen Saver", -1, -1, 499, &amp;enterScreenSaver, tm_numeric, 0, 2, 0},  // Idx 203</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A206" s="16">
+        <f t="shared" si="55"/>
+        <v>204</v>
+      </c>
+      <c r="B206" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C206" s="13">
+        <v>-1</v>
+      </c>
+      <c r="D206" s="13">
+        <v>-1</v>
+      </c>
+      <c r="E206" s="13"/>
+      <c r="F206" s="7">
+        <v>0</v>
+      </c>
+      <c r="G206" s="7">
+        <v>1</v>
+      </c>
+      <c r="H206" s="7">
+        <v>0</v>
+      </c>
+      <c r="I206" s="18">
+        <v>-1</v>
+      </c>
+      <c r="J206" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K206" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="L206" s="11" t="str">
+        <f t="shared" si="53"/>
         <v xml:space="preserve">"Bootld Update", </v>
       </c>
-      <c r="M205" s="11" t="str">
+      <c r="M206" s="11" t="str">
+        <f t="shared" si="54"/>
+        <v xml:space="preserve">&amp;enterBootloader, </v>
+      </c>
+      <c r="N206" s="11" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">tm_button, </v>
+      </c>
+      <c r="O206" s="10" t="str">
+        <f t="shared" ref="O206:O207" si="60">CONCATENATE("  {",L206,C206,", ",D206,", ",I206,", ",M206,N206,F206,", ",G206,", ",H206,"},  // Idx ", A206)</f>
+        <v xml:space="preserve">  {"Bootld Update", -1, -1, -1, &amp;enterBootloader, tm_button, 0, 1, 0},  // Idx 204</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="16">
+        <f t="shared" ref="A207" si="61">A206+1</f>
+        <v>205</v>
+      </c>
+      <c r="B207" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="C207" s="13">
+        <v>-1</v>
+      </c>
+      <c r="D207" s="13">
+        <v>-1</v>
+      </c>
+      <c r="E207" s="13"/>
+      <c r="F207" s="2">
+        <v>0</v>
+      </c>
+      <c r="G207" s="4">
+        <v>2</v>
+      </c>
+      <c r="H207" s="7">
+        <v>0</v>
+      </c>
+      <c r="I207" s="18">
+        <v>496</v>
+      </c>
+      <c r="J207" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="K207" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="L207" s="11" t="str">
         <f t="shared" si="53"/>
-        <v xml:space="preserve">&amp;enterBootloader, </v>
-      </c>
-      <c r="N205" s="11" t="str">
-        <f t="shared" si="48"/>
-        <v xml:space="preserve">tm_button, </v>
-      </c>
-      <c r="O205" s="10" t="str">
-        <f t="shared" ref="O205:O236" si="55">CONCATENATE("  {",L205,C205,", ",D205,", ",I205,", ",M205,N205,F205,", ",G205,", ",H205,"},  // Idx ", A205)</f>
-        <v xml:space="preserve">  {"Bootld Update", -1, -1, -1, &amp;enterBootloader, tm_button, 0, 1, 0},  // Idx 203</v>
-      </c>
-    </row>
-    <row r="206" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="16">
-        <f t="shared" ref="A206" si="56">A205+1</f>
-        <v>204</v>
-      </c>
-      <c r="B206" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="C206" s="13">
-        <v>-1</v>
-      </c>
-      <c r="D206" s="13">
-        <v>-1</v>
-      </c>
-      <c r="E206" s="13"/>
-      <c r="F206" s="2">
-        <v>0</v>
-      </c>
-      <c r="G206" s="4">
-        <v>2</v>
-      </c>
-      <c r="H206" s="7">
-        <v>0</v>
-      </c>
-      <c r="I206" s="18">
-        <v>496</v>
-      </c>
-      <c r="J206" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="K206" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="L206" s="11" t="str">
-        <f t="shared" si="52"/>
         <v xml:space="preserve">"WiFi Mode", </v>
       </c>
-      <c r="M206" s="11" t="str">
-        <f t="shared" si="53"/>
+      <c r="M207" s="11" t="str">
+        <f t="shared" si="54"/>
         <v xml:space="preserve">&amp;saveWifi, </v>
       </c>
-      <c r="N206" s="11" t="str">
-        <f t="shared" si="48"/>
+      <c r="N207" s="11" t="str">
+        <f t="shared" si="49"/>
         <v xml:space="preserve">tm_wifimode, </v>
       </c>
-      <c r="O206" s="10" t="str">
-        <f t="shared" si="55"/>
-        <v xml:space="preserve">  {"WiFi Mode", -1, -1, 496, &amp;saveWifi, tm_wifimode, 0, 2, 0},  // Idx 204</v>
-      </c>
-    </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A207" s="19">
-        <f>A206+1</f>
-        <v>205</v>
-      </c>
-      <c r="C207" s="17"/>
-      <c r="D207" s="17"/>
-      <c r="E207" s="17"/>
-      <c r="F207" s="19"/>
-      <c r="G207" s="19"/>
-      <c r="H207" s="19"/>
-      <c r="I207" s="19"/>
-      <c r="O207" s="7" t="s">
+      <c r="O207" s="10" t="str">
+        <f t="shared" si="60"/>
+        <v xml:space="preserve">  {"WiFi Mode", -1, -1, 496, &amp;saveWifi, tm_wifimode, 0, 2, 0},  // Idx 205</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A208" s="19">
+        <f>A207+1</f>
+        <v>206</v>
+      </c>
+      <c r="C208" s="17"/>
+      <c r="D208" s="17"/>
+      <c r="E208" s="17"/>
+      <c r="F208" s="19"/>
+      <c r="G208" s="19"/>
+      <c r="H208" s="19"/>
+      <c r="I208" s="19"/>
+      <c r="O208" s="7" t="s">
         <v>2</v>
       </c>
     </row>
